--- a/inventory_updated.xlsx
+++ b/inventory_updated.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rb4bfbeffe49546ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R3708e5eb08d04dd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R5ae1c0c1e55946fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R145bbb1ada274298"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R9cf38189a79f4ef0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Rbb63a3d43cb64647"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R36b4a11ed88e41df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Rf12a425d86334299"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="Ra9bb953a0af84382"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="R8a8ebeb1a8ec4af3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="R34027f8d74174b93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Rd6e71f67630f46a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="Rba6ed59194c349c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="R4b780221d4b54d0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R29aac592780e4f17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="Rd5925f4951ce4421"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="Rff71a3706635479f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R14033148669b46ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="Rb997ce8408444e57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Ree424ff84e1c46c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="Rc9800a15c885496b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Rd6d438c8d2294556"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R84e75b7e9cf2454c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="R21d0f75dae5846f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="R04bbf0c8b5d74962"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Rcf3e3319e5c8474f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R1c8fa8aa887c46a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="R04dbc4c020704a06"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3488,7 +3488,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R57b3904fa9394607"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R31e06aa10fe14883"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3518,7 +3518,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1313e585e32d470b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R269a0217e9364b79"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3545,7 +3545,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R944c2394077348c6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb48954dd02cc443c"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3577,7 +3577,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R6d021d31378447df"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra013f4990da945a5"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3609,7 +3609,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rc6da2910f16e4d17"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R215515f500e540ec"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4017,7 +4017,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="504" t="str">
-        <x:v>ADAMAX, AOD-9604, BPC-157, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, GHK-Cu, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
+        <x:v>AOD-9604, BPC-157, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, GHK-Cu, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
       </x:c>
       <x:c r="D4" s="505"/>
       <x:c r="E4" s="504"/>
@@ -4457,7 +4457,7 @@
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31c2f82354d44cb9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40bd801276994603"/>
 </x:worksheet>
 </file>
 
@@ -10333,7 +10333,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c63644e0fdf4bad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdabe0008ebd94550"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10351,7 +10351,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R159a241aed724372"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d4ef11739ae4229"/>
 </x:worksheet>
 </file>
 
@@ -10368,7 +10368,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc23dce935a214d65"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf08d1d87e47c478b"/>
 </x:worksheet>
 </file>
 
@@ -10385,7 +10385,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R487008a0337e4681"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab36998840764121"/>
 </x:worksheet>
 </file>
 
@@ -13020,7 +13020,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98a1ce4d38aa4d87"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e7eabee7d0d4d35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14648,7 +14648,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3fcc15d35c64cae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d493820e4454632"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17240,7 +17240,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf783101a754048e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e0eb26b5ac74d96"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22976,7 +22976,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R552503acab4a4aad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re52e84e75b934256"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25237,7 +25237,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R965852fb50a248c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00f4c62250c54c7b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27615,7 +27615,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ef287a08a88435f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb240580d97144a2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/inventory_updated.xlsx
+++ b/inventory_updated.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R29aac592780e4f17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="Rd5925f4951ce4421"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="Rff71a3706635479f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R14033148669b46ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="Rb997ce8408444e57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Ree424ff84e1c46c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="Rc9800a15c885496b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Rd6d438c8d2294556"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R84e75b7e9cf2454c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="R21d0f75dae5846f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="R04bbf0c8b5d74962"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Rcf3e3319e5c8474f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R1c8fa8aa887c46a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="R04dbc4c020704a06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rb4bfbeffe49546ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R3708e5eb08d04dd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R5ae1c0c1e55946fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R145bbb1ada274298"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R9cf38189a79f4ef0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Rbb63a3d43cb64647"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R36b4a11ed88e41df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Rf12a425d86334299"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="Ra9bb953a0af84382"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="R8a8ebeb1a8ec4af3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="R34027f8d74174b93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Rd6e71f67630f46a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="Rba6ed59194c349c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="R4b780221d4b54d0b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3488,7 +3488,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R31e06aa10fe14883"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R57b3904fa9394607"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3518,7 +3518,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R269a0217e9364b79"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1313e585e32d470b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3545,7 +3545,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb48954dd02cc443c"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R944c2394077348c6"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3577,7 +3577,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra013f4990da945a5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R6d021d31378447df"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3609,7 +3609,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R215515f500e540ec"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rc6da2910f16e4d17"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4017,7 +4017,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="504" t="str">
-        <x:v>AOD-9604, BPC-157, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, GHK-Cu, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
+        <x:v>ADAMAX, AOD-9604, BPC-157, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, GHK-Cu, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
       </x:c>
       <x:c r="D4" s="505"/>
       <x:c r="E4" s="504"/>
@@ -4457,7 +4457,7 @@
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40bd801276994603"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31c2f82354d44cb9"/>
 </x:worksheet>
 </file>
 
@@ -10333,7 +10333,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdabe0008ebd94550"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c63644e0fdf4bad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10351,7 +10351,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d4ef11739ae4229"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R159a241aed724372"/>
 </x:worksheet>
 </file>
 
@@ -10368,7 +10368,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf08d1d87e47c478b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc23dce935a214d65"/>
 </x:worksheet>
 </file>
 
@@ -10385,7 +10385,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab36998840764121"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R487008a0337e4681"/>
 </x:worksheet>
 </file>
 
@@ -13020,7 +13020,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e7eabee7d0d4d35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98a1ce4d38aa4d87"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14648,7 +14648,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d493820e4454632"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3fcc15d35c64cae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17240,7 +17240,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e0eb26b5ac74d96"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf783101a754048e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22976,7 +22976,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re52e84e75b934256"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R552503acab4a4aad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25237,7 +25237,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00f4c62250c54c7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R965852fb50a248c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27615,7 +27615,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb240580d97144a2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ef287a08a88435f"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/inventory_updated.xlsx
+++ b/inventory_updated.xlsx
@@ -2,21 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R9a57115593144bc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R09c2aef054de40b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R54f22b2469d3495c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R2df777c2adbc49f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="Rec60466cd9b041f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="R7eb5f581997545d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="Rcdbeae5a24e04461"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Rfaedff6539644979"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R4d4281ce4e8e4e80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="Rce927b5869074e0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="R901d63e8046f4862"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Rb2afc199460e4d2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R2e7f3198d2204c4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="R44eb7677bc934ae4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R2a1d615cf7604b2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbbf8fff600fa4d6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R3b78202dc6a74ae5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R6fc2db3548414f01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R97da5e87ee3e4b0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R9b7a4f4d30874686"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="R4c79e0b8ac2145e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="Rd217690a545542c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Raaa96cd61291447f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="Rc5187fbaeab140b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="Rf2f7610cb59348a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="Reb2df176e9ba4a8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Rb1515e023dc44e20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R3d22b3c1193646a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="Rf5e741a1ac4b4ee9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R09ba65a46f1a451c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="Rf14273d99b9a45be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="R4f01d343e87a4100"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="R5a5a8e506bc047e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="Rc266f040c8574520"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="Rb630cf48e01e4bf3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R189b65b697ef4cae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R39f494d027354ce4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="Ra49c5376f63a4ace"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -302,7 +310,7 @@
         <x:v>Total COA Records</x:v>
       </x:c>
       <x:c r="B3" s="14" t="n">
-        <x:v>36</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
         <x:v>Synced from COA Database</x:v>
@@ -315,10 +323,10 @@
         <x:v>Unique Peptides</x:v>
       </x:c>
       <x:c r="B4" s="14" t="n">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>ADAMAX, AOD-9604, BPC-157, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, GHK-Cu, KLOW 80mg, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
+        <x:v>ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, Eloralintide, GHK-Cu, Ipamorelin, KLOW 80mg, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
       </x:c>
       <x:c r="D4" s="14"/>
       <x:c r="E4" s="14"/>
@@ -328,7 +336,7 @@
         <x:v>Average Purity %</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:v>99.647</x:v>
+        <x:v>99.613</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
         <x:v>Populated purity results</x:v>
@@ -341,7 +349,7 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C6" s="14"/>
       <x:c r="D6" s="14"/>
@@ -352,7 +360,7 @@
         <x:v>Underfilled</x:v>
       </x:c>
       <x:c r="B7" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="14"/>
       <x:c r="D7" s="14"/>
@@ -363,7 +371,7 @@
         <x:v>On Label/Review</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="14"/>
       <x:c r="D8" s="14"/>
@@ -374,10 +382,10 @@
         <x:v>Labs Used</x:v>
       </x:c>
       <x:c r="B9" s="14" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>Aminos Analytics, BT Labs, Freedom Diagnostics, Janoshik, Kovera Labs, SteriGenix, Testides</x:v>
+        <x:v>Aminos Analytics, BT Labs, Freedom Diagnostics, Janoshik, Kovera Labs, SteriGenix, Testides, Tianjin Qiangxin (third-party partner lab)</x:v>
       </x:c>
       <x:c r="D9" s="14"/>
       <x:c r="E9" s="14"/>
@@ -387,7 +395,7 @@
         <x:v>Latest COA Date</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="C10" s="14"/>
       <x:c r="D10" s="14"/>
@@ -419,129 +427,135 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="14" t="str">
-        <x:v>COA-0036</x:v>
+        <x:v>COA-0043</x:v>
       </x:c>
       <x:c r="B13" s="14" t="str">
-        <x:v>KLOW 80mg</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="D13" s="14" t="n">
-        <x:v>99.82</x:v>
+        <x:v>99.41</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Clear</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="14" t="str">
-        <x:v>COA-0035</x:v>
+        <x:v>COA-0042</x:v>
       </x:c>
       <x:c r="B14" s="14" t="str">
-        <x:v>GHK-Cu</x:v>
+        <x:v>Ipamorelin</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="D14" s="14" t="n">
-        <x:v>99.77</x:v>
+        <x:v>99.34</x:v>
       </x:c>
       <x:c r="E14" s="14" t="str">
-        <x:v>Clear/Transparent</x:v>
+        <x:v>White</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="14" t="str">
-        <x:v>COA-0024</x:v>
+        <x:v>COA-0041</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="D15" s="14" t="n">
-        <x:v>99.86</x:v>
+        <x:v>99.78</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
-        <x:v>Clear Green</x:v>
+        <x:v>Blue</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="14" t="str">
-        <x:v>COA-0004</x:v>
+        <x:v>COA-0040</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>BPC-157</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="D16" s="14" t="n">
-        <x:v>99.491</x:v>
+        <x:v>99.57</x:v>
       </x:c>
       <x:c r="E16" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Green</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="14" t="str">
-        <x:v>COA-0003</x:v>
+        <x:v>COA-0039</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Semaglutide</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="D17" s="14" t="n">
-        <x:v>99.654</x:v>
+        <x:v>99.32</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="14" t="str">
-        <x:v>COA-0001</x:v>
-      </x:c>
-      <x:c r="B18" s="14"/>
-      <x:c r="C18" s="14"/>
-      <x:c r="D18" s="14"/>
+        <x:v>COA-0038</x:v>
+      </x:c>
+      <x:c r="B18" s="14" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="n">
+        <x:v>99.52</x:v>
+      </x:c>
       <x:c r="E18" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="14" t="str">
-        <x:v>COA-0012</x:v>
+        <x:v>COA-0037</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>AOD-9604</x:v>
+        <x:v>BPC-157 / TB-500 Blend</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="D19" s="14" t="n">
-        <x:v>99.883</x:v>
+        <x:v>99.13</x:v>
       </x:c>
       <x:c r="E19" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Red</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="14" t="str">
-        <x:v>COA-0021</x:v>
+        <x:v>COA-0044</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>CJC-1295 No DAC</x:v>
+        <x:v>Eloralintide</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
       </x:c>
       <x:c r="D20" s="14" t="n">
-        <x:v>99.897</x:v>
+        <x:v>99.67</x:v>
       </x:c>
       <x:c r="E20" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -549,16 +563,16 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="14" t="str">
-        <x:v>COA-0022</x:v>
+        <x:v>COA-0004</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
         <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="D21" s="14" t="n">
-        <x:v>99.825</x:v>
+        <x:v>99.491</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -566,16 +580,16 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="14" t="str">
-        <x:v>COA-0023</x:v>
+        <x:v>COA-0003</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="D22" s="14" t="n">
-        <x:v>99.731</x:v>
+        <x:v>99.654</x:v>
       </x:c>
       <x:c r="E22" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -583,16 +597,16 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="14" t="str">
-        <x:v>COA-0011</x:v>
+        <x:v>COA-0023</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D23" s="14" t="n">
-        <x:v>99.04</x:v>
+        <x:v>99.731</x:v>
       </x:c>
       <x:c r="E23" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -600,16 +614,16 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="14" t="str">
-        <x:v>COA-0014</x:v>
+        <x:v>COA-0022</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D24" s="14" t="n">
-        <x:v>99.055</x:v>
+        <x:v>99.825</x:v>
       </x:c>
       <x:c r="E24" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -617,16 +631,16 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="14" t="str">
-        <x:v>COA-0016</x:v>
+        <x:v>COA-0021</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>CJC-1295 No DAC</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D25" s="14" t="n">
-        <x:v>99.085</x:v>
+        <x:v>99.897</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -634,16 +648,16 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="14" t="str">
-        <x:v>COA-0019</x:v>
+        <x:v>COA-0012</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>SS-31</x:v>
+        <x:v>AOD-9604</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D26" s="14" t="n">
-        <x:v>99.95</x:v>
+        <x:v>99.883</x:v>
       </x:c>
       <x:c r="E26" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -651,16 +665,16 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="14" t="str">
-        <x:v>COA-0028</x:v>
+        <x:v>COA-0001</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
-        <x:v>BPC/TB Blend</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D27" s="14" t="n">
-        <x:v>99.81</x:v>
+        <x:v>99.516</x:v>
       </x:c>
       <x:c r="E27" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -668,16 +682,16 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="14" t="str">
-        <x:v>COA-0029</x:v>
+        <x:v>COA-0019</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>SS-31</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D28" s="14" t="n">
-        <x:v>99.39</x:v>
+        <x:v>99.95</x:v>
       </x:c>
       <x:c r="E28" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -685,16 +699,16 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="14" t="str">
-        <x:v>COA-0030</x:v>
+        <x:v>COA-0016</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>TB-500</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D29" s="14" t="n">
-        <x:v>99.49</x:v>
+        <x:v>99.085</x:v>
       </x:c>
       <x:c r="E29" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -702,16 +716,16 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="14" t="str">
-        <x:v>COA-0031</x:v>
+        <x:v>COA-0014</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D30" s="14" t="n">
-        <x:v>99.58</x:v>
+        <x:v>99.055</x:v>
       </x:c>
       <x:c r="E30" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -719,54 +733,44 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="14" t="str">
-        <x:v>COA-0032</x:v>
+        <x:v>COA-0011</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
-        <x:v>Semaglutide</x:v>
+        <x:v>Cagrilintide</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D31" s="14" t="n">
-        <x:v>99.642</x:v>
+        <x:v>99.04</x:v>
       </x:c>
       <x:c r="E31" s="14" t="str">
-        <x:v>Black</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="14" t="str">
-        <x:v>COA-0033</x:v>
+        <x:v>COA-0006</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Aminos Analytics</x:v>
       </x:c>
       <x:c r="D32" s="14" t="n">
-        <x:v>99.6</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="E32" s="14" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="14" t="str">
-        <x:v>COA-0034</x:v>
-      </x:c>
-      <x:c r="B33" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
-      </x:c>
-      <x:c r="C33" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="D33" s="14" t="n">
-        <x:v>99.747</x:v>
-      </x:c>
-      <x:c r="E33" s="14" t="str">
-        <x:v>Purple</x:v>
-      </x:c>
+      <x:c r="A33" s="14"/>
+      <x:c r="B33" s="14"/>
+      <x:c r="C33" s="14"/>
+      <x:c r="D33" s="14"/>
+      <x:c r="E33" s="14"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -853,7 +857,7 @@
         <x:v>Total COA/Test Records</x:v>
       </x:c>
       <x:c r="B3" s="14" t="n">
-        <x:v>36</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
         <x:v>All records from COA Database</x:v>
@@ -1015,7 +1019,7 @@
         <x:v>Average Purity %</x:v>
       </x:c>
       <x:c r="B9" s="14" t="n">
-        <x:v>99.647</x:v>
+        <x:v>99.613</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
         <x:v>Based on populated purity values</x:v>
@@ -5555,6 +5559,586 @@
       </x:c>
       <x:c r="B23" s="14" t="str">
         <x:v>assets/coa/KLOW80mg-02.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>BPC-157 / TB-500 Blend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Healing / Recovery Blend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>RPT-2026-237183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>SGX-VP-2026-0728-G37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>BB260725A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>10.55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Red</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/COA RPT-2026-237183 - SteriGenix.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0038</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>RPT-2026-442015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>SGX-VP-2026-0728-K72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>TR260725A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>10.09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Yellow</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/COA RPT-2026-442015 - SteriGenix.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>RPT-2026-538821</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>SGX-VP-2026-0728-U17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>SM260725A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/COA RPT-2026-538821 - SteriGenix.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0040</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>RPT-2026-654610</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>SGX-VP-2026-0728-Z53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>BC260725A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>5.13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Green</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/COA RPT-2026-654610 - SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7797,7 +8381,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P33" s="14" t="str">
-        <x:v>Local image: assets/coa/photo_2026-07-04_22-14-31.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Semaglutide 15mg)</x:v>
       </x:c>
       <x:c r="Q33" s="14" t="str">
         <x:v>Pass</x:v>
@@ -7865,7 +8449,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P34" s="14" t="str">
-        <x:v>Local image: assets/coa/photo_2026-07-04_22-34-37.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 30mg)</x:v>
       </x:c>
       <x:c r="Q34" s="14" t="str">
         <x:v>Pass</x:v>
@@ -7933,7 +8517,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P35" s="14" t="str">
-        <x:v>Local image: assets/coa/photo_2026-07-04_22-35-21.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 15mg)</x:v>
       </x:c>
       <x:c r="Q35" s="14" t="str">
         <x:v>Pass</x:v>
@@ -8001,7 +8585,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P36" s="14" t="str">
-        <x:v>Local image: assets/coa/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
+        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
       </x:c>
       <x:c r="Q36" s="14" t="str">
         <x:v>Pass</x:v>
@@ -8088,6 +8672,1130 @@
       </x:c>
       <x:c r="V37" s="14" t="str">
         <x:v>Yellow flip-off cap with silver aluminum crimp, based on the vial image shown on page 1 of the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>BPC-157 / TB-500 Blend</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Healing / Recovery Blend</x:v>
+      </x:c>
+      <x:c r="D38" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E38" t="n">
+        <x:v>10.55</x:v>
+      </x:c>
+      <x:c r="F38" t="n">
+        <x:v>0.5500000000000007</x:v>
+      </x:c>
+      <x:c r="G38" t="n">
+        <x:v>0.05500000000000007</x:v>
+      </x:c>
+      <x:c r="H38" t="n">
+        <x:v>99.13</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L38" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>RPT-2026-237183</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>SGX-VP-2026-0728-G37</x:v>
+      </x:c>
+      <x:c r="O38" t="str">
+        <x:v>BB260725A</x:v>
+      </x:c>
+      <x:c r="P38" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q38" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R38" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S38" t="str">
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T38" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U38" t="str">
+        <x:v>Red</x:v>
+      </x:c>
+      <x:c r="V38" t="str">
+        <x:v>Red flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>COA-0038</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D39" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E39" t="n">
+        <x:v>10.09</x:v>
+      </x:c>
+      <x:c r="F39" t="n">
+        <x:v>0.08999999999999986</x:v>
+      </x:c>
+      <x:c r="G39" t="n">
+        <x:v>0.008999999999999985</x:v>
+      </x:c>
+      <x:c r="H39" t="n">
+        <x:v>99.52</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K39" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L39" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>RPT-2026-442015</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>SGX-VP-2026-0728-K72</x:v>
+      </x:c>
+      <x:c r="O39" t="str">
+        <x:v>TR260725A</x:v>
+      </x:c>
+      <x:c r="P39" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q39" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R39" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S39" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T39" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U39" t="str">
+        <x:v>Yellow</x:v>
+      </x:c>
+      <x:c r="V39" t="str">
+        <x:v>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D40" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E40" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="F40" t="n">
+        <x:v>0.07000000000000028</x:v>
+      </x:c>
+      <x:c r="G40" t="n">
+        <x:v>0.014000000000000058</x:v>
+      </x:c>
+      <x:c r="H40" t="n">
+        <x:v>99.32</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K40" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L40" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>RPT-2026-538821</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>SGX-VP-2026-0728-U17</x:v>
+      </x:c>
+      <x:c r="O40" t="str">
+        <x:v>SM260725A</x:v>
+      </x:c>
+      <x:c r="P40" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q40" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R40" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S40" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T40" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U40" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="V40" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>COA-0040</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="D41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E41" t="n">
+        <x:v>5.13</x:v>
+      </x:c>
+      <x:c r="F41" t="n">
+        <x:v>0.1299999999999999</x:v>
+      </x:c>
+      <x:c r="G41" t="n">
+        <x:v>0.025999999999999978</x:v>
+      </x:c>
+      <x:c r="H41" t="n">
+        <x:v>99.57</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K41" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L41" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M41" t="str">
+        <x:v>RPT-2026-654610</x:v>
+      </x:c>
+      <x:c r="N41" t="str">
+        <x:v>SGX-VP-2026-0728-Z53</x:v>
+      </x:c>
+      <x:c r="O41" t="str">
+        <x:v>BC260725A</x:v>
+      </x:c>
+      <x:c r="P41" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q41" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R41" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S41" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T41" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U41" t="str">
+        <x:v>Green</x:v>
+      </x:c>
+      <x:c r="V41" t="str">
+        <x:v>Green flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>COA-0041</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D42" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E42" t="n">
+        <x:v>51.34</x:v>
+      </x:c>
+      <x:c r="F42" t="n">
+        <x:v>1.3400000000000034</x:v>
+      </x:c>
+      <x:c r="G42" t="n">
+        <x:v>0.026800000000000067</x:v>
+      </x:c>
+      <x:c r="H42" t="n">
+        <x:v>99.78</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K42" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L42" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M42" t="str">
+        <x:v>RPT-2026-697297</x:v>
+      </x:c>
+      <x:c r="N42" t="str">
+        <x:v>SGX-VP-2026-0728-K16</x:v>
+      </x:c>
+      <x:c r="O42" t="str">
+        <x:v>CU260725A</x:v>
+      </x:c>
+      <x:c r="P42" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q42" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R42" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S42" t="str">
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T42" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U42" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="V42" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Ipamorelin</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Growth Hormone Support</x:v>
+      </x:c>
+      <x:c r="D43" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E43" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+      <x:c r="F43" t="n">
+        <x:v>0.16999999999999993</x:v>
+      </x:c>
+      <x:c r="G43" t="n">
+        <x:v>0.03399999999999999</x:v>
+      </x:c>
+      <x:c r="H43" t="n">
+        <x:v>99.34</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K43" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L43" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M43" t="str">
+        <x:v>RPT-2026-822844</x:v>
+      </x:c>
+      <x:c r="N43" t="str">
+        <x:v>SGX-VP-2026-0728-U21</x:v>
+      </x:c>
+      <x:c r="O43" t="str">
+        <x:v>IP260725A</x:v>
+      </x:c>
+      <x:c r="P43" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q43" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R43" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S43" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T43" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U43" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="V43" t="str">
+        <x:v>White flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>COA-0043</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D44" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E44" t="n">
+        <x:v>10.36</x:v>
+      </x:c>
+      <x:c r="F44" t="n">
+        <x:v>0.35999999999999943</x:v>
+      </x:c>
+      <x:c r="G44" t="n">
+        <x:v>0.03599999999999994</x:v>
+      </x:c>
+      <x:c r="H44" t="n">
+        <x:v>99.41</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K44" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L44" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M44" t="str">
+        <x:v>RPT-2026-932680</x:v>
+      </x:c>
+      <x:c r="N44" t="str">
+        <x:v>SGX-VP-2026-0728-G60</x:v>
+      </x:c>
+      <x:c r="O44" t="str">
+        <x:v>RT260725A</x:v>
+      </x:c>
+      <x:c r="P44" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q44" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R44" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S44" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T44" t="str">
+        <x:v>Copper</x:v>
+      </x:c>
+      <x:c r="U44" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="V44" t="str">
+        <x:v>Clear flip-off cap with copper aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>COA-0044</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Amylin / Weight</x:v>
+      </x:c>
+      <x:c r="D45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E45" t="n">
+        <x:v>4.63</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>-0.3700000000000001</x:v>
+      </x:c>
+      <x:c r="G45" t="n">
+        <x:v>-0.07400000000000002</x:v>
+      </x:c>
+      <x:c r="H45" t="n">
+        <x:v>99.67</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>Underfilled</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>Report reviewed</x:v>
+      </x:c>
+      <x:c r="L45" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>Elor5-20260731S0925</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="O45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="P45" t="str">
+        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+      </x:c>
+      <x:c r="Q45" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R45" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S45" t="str">
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+      </x:c>
+      <x:c r="T45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="U45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="V45" t="str">
+        <x:v>Crimp/cap color not listed in the testing record.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0041</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>RPT-2026-697297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>SGX-VP-2026-0728-K16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>CU260725A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>51.34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/COA RPT-2026-697297 - SteriGenix.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Ipamorelin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Growth Hormone Support</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>RPT-2026-822844</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>SGX-VP-2026-0728-U21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>IP260725A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>White</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/COA RPT-2026-822844 - SteriGenix.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0043</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>RPT-2026-932680</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>SGX-VP-2026-0728-G60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>RT260725A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>10.36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Copper</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/COA RPT-2026-932680 - SteriGenix.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0044</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Eloralintide</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Amylin / Weight</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Elor5-20260731S0925</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>4.63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Underfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/Elor5-20260731S0925_report.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8736,43 +10444,43 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>COA-0035</x:v>
+        <x:v>COA-0041</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
         <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>Regenerative / Skin</x:v>
+        <x:v>Cosmetic / Recovery</x:v>
       </x:c>
       <x:c r="E15" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="F15" s="14" t="n">
-        <x:v>50.75</x:v>
+        <x:v>51.34</x:v>
       </x:c>
       <x:c r="G15" s="16" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.026800000000000067</x:v>
       </x:c>
       <x:c r="H15" s="18" t="n">
-        <x:v>99.77</x:v>
+        <x:v>99.78</x:v>
       </x:c>
       <x:c r="I15" s="14" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J15" s="14" t="str">
-        <x:v>Freedom Diagnostics</x:v>
-      </x:c>
-      <x:c r="K15" s="14" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L15" s="14" t="str">
-        <x:v>Clear/Transparent</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M15" s="14" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N15" s="14" t="str">
-        <x:v>GHK-Cu 50mg; identity confirmed; blue lyophilized powder; received 06/26/2026; reported 06/29/2026.</x:v>
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -8780,43 +10488,43 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>COA-0034</x:v>
+        <x:v>COA-0035</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D16" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Regenerative / Skin</x:v>
       </x:c>
       <x:c r="E16" s="14" t="n">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F16" s="14" t="n">
-        <x:v>15.59</x:v>
+        <x:v>50.75</x:v>
       </x:c>
       <x:c r="G16" s="16" t="n">
-        <x:v>0.03933333333333333</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="H16" s="18" t="n">
-        <x:v>99.747</x:v>
+        <x:v>99.77</x:v>
       </x:c>
       <x:c r="I16" s="14" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J16" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K16" s="14" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="L16" s="14" t="str">
-        <x:v>Purple</x:v>
+        <x:v>Clear/Transparent</x:v>
       </x:c>
       <x:c r="M16" s="14" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N16" s="14" t="str">
-        <x:v>Kovera image COA; purple cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
+        <x:v>GHK-Cu 50mg; identity confirmed; blue lyophilized powder; received 06/26/2026; reported 06/29/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -8824,7 +10532,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
-        <x:v>COA-0023</x:v>
+        <x:v>COA-0034</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
         <x:v>Tirzepatide</x:v>
@@ -8836,31 +10544,31 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F17" s="14" t="n">
-        <x:v>16.18</x:v>
+        <x:v>15.59</x:v>
       </x:c>
       <x:c r="G17" s="16" t="n">
-        <x:v>0.07866666666666665</x:v>
+        <x:v>0.03933333333333333</x:v>
       </x:c>
       <x:c r="H17" s="18" t="n">
-        <x:v>99.731</x:v>
+        <x:v>99.747</x:v>
       </x:c>
       <x:c r="I17" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J17" s="14" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K17" s="14" t="n">
-        <x:v>46156</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K17" s="14" t="str">
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L17" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Purple</x:v>
       </x:c>
       <x:c r="M17" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N17" s="14" t="str">
-        <x:v>T15 Tirzepatide 15mg; common GLP-1 blind test; overfilled.</x:v>
+        <x:v>Kovera image COA; purple cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -8868,7 +10576,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
-        <x:v>COA-0007</x:v>
+        <x:v>COA-0023</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
         <x:v>Tirzepatide</x:v>
@@ -8877,34 +10585,34 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E18" s="14" t="n">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F18" s="14" t="n">
-        <x:v>26</x:v>
+        <x:v>16.18</x:v>
       </x:c>
       <x:c r="G18" s="16" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.07866666666666665</x:v>
       </x:c>
       <x:c r="H18" s="18" t="n">
-        <x:v>99.7</x:v>
+        <x:v>99.731</x:v>
       </x:c>
       <x:c r="I18" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J18" s="14" t="str">
-        <x:v>BT Labs</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K18" s="14" t="n">
-        <x:v>46133</x:v>
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L18" s="14" t="str">
-        <x:v>Royal Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M18" s="14" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N18" s="14" t="str">
-        <x:v>20 mg label; 130.1% potency</x:v>
+        <x:v>T15 Tirzepatide 15mg; common GLP-1 blind test; overfilled.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -8912,7 +10620,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>COA-0008</x:v>
+        <x:v>COA-0007</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
         <x:v>Tirzepatide</x:v>
@@ -8921,13 +10629,13 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E19" s="14" t="n">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F19" s="14" t="n">
-        <x:v>46.6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G19" s="16" t="n">
-        <x:v>0.165</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="H19" s="18" t="n">
         <x:v>99.7</x:v>
@@ -8939,16 +10647,16 @@
         <x:v>BT Labs</x:v>
       </x:c>
       <x:c r="K19" s="14" t="n">
-        <x:v>46106</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="L19" s="14" t="str">
-        <x:v>Gray</x:v>
+        <x:v>Royal Blue</x:v>
       </x:c>
       <x:c r="M19" s="14" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N19" s="14" t="str">
-        <x:v>40 mg label; 116.4% potency</x:v>
+        <x:v>20 mg label; 130.1% potency</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -8956,43 +10664,43 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>COA-0003</x:v>
+        <x:v>COA-0008</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D20" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E20" s="14" t="n">
-        <x:v>5</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F20" s="14" t="n">
-        <x:v>6.63</x:v>
+        <x:v>46.6</x:v>
       </x:c>
       <x:c r="G20" s="16" t="n">
-        <x:v>0.326</x:v>
+        <x:v>0.165</x:v>
       </x:c>
       <x:c r="H20" s="18" t="n">
-        <x:v>99.654</x:v>
+        <x:v>99.7</x:v>
       </x:c>
       <x:c r="I20" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J20" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>BT Labs</x:v>
       </x:c>
       <x:c r="K20" s="14" t="n">
-        <x:v>46174</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L20" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Gray</x:v>
       </x:c>
       <x:c r="M20" s="14" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N20" s="14" t="str">
-        <x:v>Heavy metals negative; endotoxin pass</x:v>
+        <x:v>40 mg label; 116.4% potency</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -9000,43 +10708,43 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>COA-0032</x:v>
+        <x:v>COA-0044</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>Semaglutide</x:v>
+        <x:v>Eloralintide</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Amylin / Weight</x:v>
       </x:c>
       <x:c r="E21" s="14" t="n">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F21" s="14" t="n">
-        <x:v>15.53</x:v>
+        <x:v>4.63</x:v>
       </x:c>
       <x:c r="G21" s="16" t="n">
-        <x:v>0.035333333333333335</x:v>
+        <x:v>-0.07400000000000002</x:v>
       </x:c>
       <x:c r="H21" s="18" t="n">
-        <x:v>99.642</x:v>
+        <x:v>99.67</x:v>
       </x:c>
       <x:c r="I21" s="14" t="str">
-        <x:v>On label</x:v>
+        <x:v>Underfilled</x:v>
       </x:c>
       <x:c r="J21" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K21" s="14" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K21" s="14" t="n">
+        <x:v>46234</x:v>
       </x:c>
       <x:c r="L21" s="14" t="str">
-        <x:v>Black</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M21" s="14" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N21" s="14" t="str">
-        <x:v>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</x:v>
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -9044,25 +10752,25 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>COA-0033</x:v>
+        <x:v>COA-0003</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E22" s="14" t="n">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F22" s="14" t="n">
-        <x:v>33.24</x:v>
+        <x:v>6.63</x:v>
       </x:c>
       <x:c r="G22" s="16" t="n">
-        <x:v>0.10800000000000001</x:v>
+        <x:v>0.326</x:v>
       </x:c>
       <x:c r="H22" s="18" t="n">
-        <x:v>99.6</x:v>
+        <x:v>99.654</x:v>
       </x:c>
       <x:c r="I22" s="14" t="str">
         <x:v>Overfilled</x:v>
@@ -9070,17 +10778,17 @@
       <x:c r="J22" s="14" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
-      <x:c r="K22" s="14" t="str">
-        <x:v>2026-07-03</x:v>
+      <x:c r="K22" s="14" t="n">
+        <x:v>46174</x:v>
       </x:c>
       <x:c r="L22" s="14" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M22" s="14" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N22" s="14" t="str">
-        <x:v>Kovera image COA; blue cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
+        <x:v>Heavy metals negative; endotoxin pass</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -9088,43 +10796,43 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>COA-0020</x:v>
+        <x:v>COA-0032</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>KPV</x:v>
+        <x:v>Semaglutide</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
-        <x:v>Other</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E23" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F23" s="14" t="n">
-        <x:v>12.19</x:v>
+        <x:v>15.53</x:v>
       </x:c>
       <x:c r="G23" s="16" t="n">
-        <x:v>0.2189999999999999</x:v>
+        <x:v>0.035333333333333335</x:v>
       </x:c>
       <x:c r="H23" s="18" t="n">
-        <x:v>99.589</x:v>
+        <x:v>99.642</x:v>
       </x:c>
       <x:c r="I23" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J23" s="14" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K23" s="14" t="n">
-        <x:v>46057</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K23" s="14" t="str">
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L23" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M23" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N23" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -9132,10 +10840,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
-        <x:v>COA-0031</x:v>
+        <x:v>COA-0033</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
@@ -9144,31 +10852,31 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="F24" s="14" t="n">
-        <x:v>33.77</x:v>
+        <x:v>33.24</x:v>
       </x:c>
       <x:c r="G24" s="16" t="n">
-        <x:v>0.12566666666666668</x:v>
+        <x:v>0.10800000000000001</x:v>
       </x:c>
       <x:c r="H24" s="18" t="n">
-        <x:v>99.58</x:v>
+        <x:v>99.6</x:v>
       </x:c>
       <x:c r="I24" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J24" s="14" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K24" s="14" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L24" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M24" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N24" s="14" t="str">
-        <x:v>Retatrutide 30mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Kovera image COA; blue cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -9176,43 +10884,43 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>COA-0026</x:v>
+        <x:v>COA-0020</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>KPV</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Other</x:v>
       </x:c>
       <x:c r="E25" s="14" t="n">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F25" s="14" t="n">
-        <x:v>42.53</x:v>
+        <x:v>12.19</x:v>
       </x:c>
       <x:c r="G25" s="16" t="n">
-        <x:v>0.06325</x:v>
+        <x:v>0.2189999999999999</x:v>
       </x:c>
       <x:c r="H25" s="18" t="n">
-        <x:v>99.569</x:v>
+        <x:v>99.589</x:v>
       </x:c>
       <x:c r="I25" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J25" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K25" s="14" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K25" s="14" t="n">
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L25" s="14" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M25" s="14" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N25" s="14" t="str">
-        <x:v>Blue cap Retatrutide 40mg</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -9220,7 +10928,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>COA-0025</x:v>
+        <x:v>COA-0031</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -9232,31 +10940,31 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="F26" s="14" t="n">
-        <x:v>33.31</x:v>
+        <x:v>33.77</x:v>
       </x:c>
       <x:c r="G26" s="16" t="n">
-        <x:v>0.1103333333333333</x:v>
+        <x:v>0.12566666666666668</x:v>
       </x:c>
       <x:c r="H26" s="18" t="n">
-        <x:v>99.563</x:v>
+        <x:v>99.58</x:v>
       </x:c>
       <x:c r="I26" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J26" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Testides</x:v>
       </x:c>
       <x:c r="K26" s="14" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L26" s="14" t="str">
-        <x:v>Transparent</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M26" s="14" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N26" s="14" t="str">
-        <x:v>Transparent cap Retatrutide 30mg</x:v>
+        <x:v>Retatrutide 30mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -9264,43 +10972,43 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
-        <x:v>COA-0001</x:v>
+        <x:v>COA-0040</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>BPC-157</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
       <x:c r="E27" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F27" s="14" t="n">
-        <x:v>11.8</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="G27" s="16" t="n">
-        <x:v>0.1800000000000001</x:v>
+        <x:v>0.025999999999999978</x:v>
       </x:c>
       <x:c r="H27" s="18" t="n">
-        <x:v>99.516</x:v>
+        <x:v>99.57</x:v>
       </x:c>
       <x:c r="I27" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J27" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="K27" s="14" t="n">
-        <x:v>46156</x:v>
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L27" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Green</x:v>
       </x:c>
       <x:c r="M27" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N27" s="14" t="str">
-        <x:v>RT10 - common GLP-1 blind test; overfilled</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -9308,7 +11016,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
-        <x:v>COA-0006</x:v>
+        <x:v>COA-0026</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -9316,31 +11024,35 @@
       <x:c r="D28" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
-      <x:c r="E28" s="14"/>
+      <x:c r="E28" s="14" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="F28" s="14" t="n">
-        <x:v>22.47</x:v>
-      </x:c>
-      <x:c r="G28" s="16"/>
+        <x:v>42.53</x:v>
+      </x:c>
+      <x:c r="G28" s="16" t="n">
+        <x:v>0.06325</x:v>
+      </x:c>
       <x:c r="H28" s="18" t="n">
-        <x:v>99.5</x:v>
+        <x:v>99.569</x:v>
       </x:c>
       <x:c r="I28" s="14" t="str">
-        <x:v>Review</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J28" s="14" t="str">
-        <x:v>Aminos Analytics</x:v>
-      </x:c>
-      <x:c r="K28" s="14" t="n">
-        <x:v>46146</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K28" s="14" t="str">
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="L28" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M28" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N28" s="14" t="str">
-        <x:v>Labeled quantity unclear from image</x:v>
+        <x:v>Blue cap Retatrutide 40mg</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -9348,7 +11060,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
-        <x:v>COA-0004</x:v>
+        <x:v>COA-0025</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -9357,16 +11069,16 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E29" s="14" t="n">
-        <x:v>15</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F29" s="14" t="n">
-        <x:v>17.93</x:v>
+        <x:v>33.31</x:v>
       </x:c>
       <x:c r="G29" s="16" t="n">
-        <x:v>0.1953333333333333</x:v>
+        <x:v>0.1103333333333333</x:v>
       </x:c>
       <x:c r="H29" s="18" t="n">
-        <x:v>99.491</x:v>
+        <x:v>99.563</x:v>
       </x:c>
       <x:c r="I29" s="14" t="str">
         <x:v>Overfilled</x:v>
@@ -9374,17 +11086,17 @@
       <x:c r="J29" s="14" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
-      <x:c r="K29" s="14" t="n">
-        <x:v>46175</x:v>
+      <x:c r="K29" s="14" t="str">
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="L29" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Transparent</x:v>
       </x:c>
       <x:c r="M29" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N29" s="14" t="str">
-        <x:v>Heavy metals negative; endotoxin pass</x:v>
+        <x:v>Transparent cap Retatrutide 30mg</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -9392,43 +11104,43 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
-        <x:v>COA-0030</x:v>
+        <x:v>COA-0038</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D30" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E30" s="14" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F30" s="14" t="n">
-        <x:v>21.4</x:v>
+        <x:v>10.09</x:v>
       </x:c>
       <x:c r="G30" s="16" t="n">
-        <x:v>0.06999999999999999</x:v>
+        <x:v>0.008999999999999985</x:v>
       </x:c>
       <x:c r="H30" s="18" t="n">
-        <x:v>99.49</x:v>
+        <x:v>99.52</x:v>
       </x:c>
       <x:c r="I30" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J30" s="14" t="str">
-        <x:v>Testides</x:v>
-      </x:c>
-      <x:c r="K30" s="14" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K30" s="14" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L30" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="M30" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N30" s="14" t="str">
-        <x:v>Retatrutide 20mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -9436,34 +11148,34 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
-        <x:v>COA-0029</x:v>
+        <x:v>COA-0001</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D31" s="14" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E31" s="14" t="n">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F31" s="14" t="n">
-        <x:v>45.03</x:v>
+        <x:v>11.8</x:v>
       </x:c>
       <x:c r="G31" s="16" t="n">
-        <x:v>0.12575</x:v>
+        <x:v>0.1800000000000001</x:v>
       </x:c>
       <x:c r="H31" s="18" t="n">
-        <x:v>99.39</x:v>
+        <x:v>99.516</x:v>
       </x:c>
       <x:c r="I31" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J31" s="14" t="str">
-        <x:v>Testides</x:v>
-      </x:c>
-      <x:c r="K31" s="14" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K31" s="14" t="n">
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L31" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -9472,7 +11184,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N31" s="14" t="str">
-        <x:v>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>RT10 - common GLP-1 blind test; overfilled</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -9480,7 +11192,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
-        <x:v>COA-0002</x:v>
+        <x:v>COA-0006</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -9488,26 +11200,22 @@
       <x:c r="D32" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
-      <x:c r="E32" s="14" t="n">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="E32" s="14"/>
       <x:c r="F32" s="14" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G32" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>22.47</x:v>
+      </x:c>
+      <x:c r="G32" s="16"/>
       <x:c r="H32" s="18" t="n">
-        <x:v>99.369</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="I32" s="14" t="str">
-        <x:v>On label</x:v>
+        <x:v>Review</x:v>
       </x:c>
       <x:c r="J32" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Aminos Analytics</x:v>
       </x:c>
       <x:c r="K32" s="14" t="n">
-        <x:v>46057</x:v>
+        <x:v>46146</x:v>
       </x:c>
       <x:c r="L32" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -9516,7 +11224,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N32" s="14" t="str">
-        <x:v>On label</x:v>
+        <x:v>Labeled quantity unclear from image</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -9524,34 +11232,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="14" t="str">
-        <x:v>COA-0016</x:v>
+        <x:v>COA-0004</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D33" s="14" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E33" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F33" s="14" t="n">
-        <x:v>11.38</x:v>
+        <x:v>17.93</x:v>
       </x:c>
       <x:c r="G33" s="16" t="n">
-        <x:v>0.1380000000000001</x:v>
+        <x:v>0.1953333333333333</x:v>
       </x:c>
       <x:c r="H33" s="18" t="n">
-        <x:v>99.085</x:v>
+        <x:v>99.491</x:v>
       </x:c>
       <x:c r="I33" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J33" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K33" s="14" t="n">
-        <x:v>46155</x:v>
+        <x:v>46175</x:v>
       </x:c>
       <x:c r="L33" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -9560,7 +11268,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N33" s="14" t="str">
-        <x:v>TB-500 / TB4</x:v>
+        <x:v>Heavy metals negative; endotoxin pass</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -9568,34 +11276,34 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="14" t="str">
-        <x:v>COA-0014</x:v>
+        <x:v>COA-0030</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D34" s="14" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E34" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F34" s="14" t="n">
-        <x:v>11.17</x:v>
+        <x:v>21.4</x:v>
       </x:c>
       <x:c r="G34" s="16" t="n">
-        <x:v>0.117</x:v>
+        <x:v>0.06999999999999999</x:v>
       </x:c>
       <x:c r="H34" s="18" t="n">
-        <x:v>99.055</x:v>
+        <x:v>99.49</x:v>
       </x:c>
       <x:c r="I34" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J34" s="14" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K34" s="14" t="n">
-        <x:v>46155</x:v>
+        <x:v>Testides</x:v>
+      </x:c>
+      <x:c r="K34" s="14" t="str">
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L34" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -9604,7 +11312,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N34" s="14" t="str">
-        <x:v>MS10 / MOTS-C</x:v>
+        <x:v>Retatrutide 20mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -9612,10 +11320,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="14" t="str">
-        <x:v>COA-0011</x:v>
+        <x:v>COA-0043</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D35" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
@@ -9624,31 +11332,467 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F35" s="14" t="n">
+        <x:v>10.36</x:v>
+      </x:c>
+      <x:c r="G35" s="16" t="n">
+        <x:v>0.03599999999999994</x:v>
+      </x:c>
+      <x:c r="H35" s="18" t="n">
+        <x:v>99.41</x:v>
+      </x:c>
+      <x:c r="I35" s="14" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J35" s="14" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K35" s="14" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L35" s="14" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="M35" s="14" t="str">
+        <x:v>Copper</x:v>
+      </x:c>
+      <x:c r="N35" s="14" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>COA-0029</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>MOTS-C</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>Metabolic / Mito</x:v>
+      </x:c>
+      <x:c r="E36" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F36" t="n">
+        <x:v>45.03</x:v>
+      </x:c>
+      <x:c r="G36" t="n">
+        <x:v>0.12575</x:v>
+      </x:c>
+      <x:c r="H36" t="n">
+        <x:v>99.39</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J36" t="str">
+        <x:v>Testides</x:v>
+      </x:c>
+      <x:c r="K36" t="str">
+        <x:v>2026-06-15</x:v>
+      </x:c>
+      <x:c r="L36" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M36" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N36" t="str">
+        <x:v>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>COA-0002</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="E37" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F37" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H37" t="n">
+        <x:v>99.369</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J37" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K37" t="n">
+        <x:v>46057</x:v>
+      </x:c>
+      <x:c r="L37" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M37" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N37" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Ipamorelin</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>Growth Hormone Support</x:v>
+      </x:c>
+      <x:c r="E38" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F38" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+      <x:c r="G38" t="n">
+        <x:v>0.03399999999999999</x:v>
+      </x:c>
+      <x:c r="H38" t="n">
+        <x:v>99.34</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K38" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L38" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="E39" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F39" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="G39" t="n">
+        <x:v>0.014000000000000058</x:v>
+      </x:c>
+      <x:c r="H39" t="n">
+        <x:v>99.32</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K39" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L39" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>BPC-157 / TB-500 Blend</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>Healing / Recovery Blend</x:v>
+      </x:c>
+      <x:c r="E40" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F40" t="n">
+        <x:v>10.55</x:v>
+      </x:c>
+      <x:c r="G40" t="n">
+        <x:v>0.05500000000000007</x:v>
+      </x:c>
+      <x:c r="H40" t="n">
+        <x:v>99.13</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K40" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L40" t="str">
+        <x:v>Red</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>COA-0016</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>TB-500</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="E41" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F41" t="n">
+        <x:v>11.38</x:v>
+      </x:c>
+      <x:c r="G41" t="n">
+        <x:v>0.1380000000000001</x:v>
+      </x:c>
+      <x:c r="H41" t="n">
+        <x:v>99.085</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K41" t="n">
+        <x:v>46155</x:v>
+      </x:c>
+      <x:c r="L41" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M41" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N41" t="str">
+        <x:v>TB-500 / TB4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>COA-0014</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>MOTS-C</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>Metabolic / Mito</x:v>
+      </x:c>
+      <x:c r="E42" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F42" t="n">
+        <x:v>11.17</x:v>
+      </x:c>
+      <x:c r="G42" t="n">
+        <x:v>0.117</x:v>
+      </x:c>
+      <x:c r="H42" t="n">
+        <x:v>99.055</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K42" t="n">
+        <x:v>46155</x:v>
+      </x:c>
+      <x:c r="L42" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M42" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N42" t="str">
+        <x:v>MS10 / MOTS-C</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>COA-0011</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Cagrilintide</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="E43" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F43" t="n">
         <x:v>10.47</x:v>
       </x:c>
-      <x:c r="G35" s="16" t="n">
+      <x:c r="G43" t="n">
         <x:v>0.04700000000000006</x:v>
       </x:c>
-      <x:c r="H35" s="18" t="n">
+      <x:c r="H43" t="n">
         <x:v>99.04</x:v>
       </x:c>
-      <x:c r="I35" s="14" t="str">
+      <x:c r="I43" t="str">
         <x:v>On label</x:v>
       </x:c>
-      <x:c r="J35" s="14" t="str">
+      <x:c r="J43" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
-      <x:c r="K35" s="14" t="n">
+      <x:c r="K43" t="n">
         <x:v>46155</x:v>
       </x:c>
-      <x:c r="L35" s="14" t="str">
-        <x:v>Not Listed</x:v>
-      </x:c>
-      <x:c r="M35" s="14" t="str">
-        <x:v>Not Listed</x:v>
-      </x:c>
-      <x:c r="N35" s="14" t="str">
+      <x:c r="L43" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M43" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N43" t="str">
         <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>COA-0017</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="E44" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F44" t="n">
+        <x:v>5.54</x:v>
+      </x:c>
+      <x:c r="G44" t="n">
+        <x:v>0.108</x:v>
+      </x:c>
+      <x:c r="H44"/>
+      <x:c r="I44" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K44" t="n">
+        <x:v>46057</x:v>
+      </x:c>
+      <x:c r="L44" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M44" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N44" t="str">
+        <x:v>Blend report BPC5+TB5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>COA-0018</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>TB-500</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="E45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>5.43</x:v>
+      </x:c>
+      <x:c r="G45" t="n">
+        <x:v>0.08599999999999994</x:v>
+      </x:c>
+      <x:c r="H45"/>
+      <x:c r="I45" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K45" t="n">
+        <x:v>46057</x:v>
+      </x:c>
+      <x:c r="L45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>Blend report BPC5+TB5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11891,7 +14035,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P33" s="14" t="str">
-        <x:v>Local image: assets/coa/photo_2026-07-04_22-14-31.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Semaglutide 15mg)</x:v>
       </x:c>
       <x:c r="Q33" s="14" t="str">
         <x:v>Pass</x:v>
@@ -11959,7 +14103,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P34" s="14" t="str">
-        <x:v>Local image: assets/coa/photo_2026-07-04_22-34-37.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 30mg)</x:v>
       </x:c>
       <x:c r="Q34" s="14" t="str">
         <x:v>Pass</x:v>
@@ -12027,7 +14171,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P35" s="14" t="str">
-        <x:v>Local image: assets/coa/photo_2026-07-04_22-35-21.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 15mg)</x:v>
       </x:c>
       <x:c r="Q35" s="14" t="str">
         <x:v>Pass</x:v>
@@ -12095,13 +14239,13 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P36" s="14" t="str">
-        <x:v>Local image: assets/coa/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
+        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
       </x:c>
       <x:c r="Q36" s="14" t="str">
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="R36" s="14" t="str">
-        <x:v>Unique Freedom Diagnostics GHK-Cu 50mg COA; no exact duplicate by compound/lab/date/content.</x:v>
+        <x:v>Append-only: independent test record retained; never overwrite or remove records based only on peptide name.</x:v>
       </x:c>
       <x:c r="S36" s="14" t="str">
         <x:v>GHK-Cu 50mg; identity confirmed; blue lyophilized powder; received 06/26/2026; reported 06/29/2026.</x:v>
@@ -12182,6 +14326,550 @@
       </x:c>
       <x:c r="V37" s="14" t="str">
         <x:v>Yellow flip-off cap with silver aluminum crimp, based on the vial image shown on page 1 of the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>BPC-157 / TB-500 Blend</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Healing / Recovery Blend</x:v>
+      </x:c>
+      <x:c r="D38" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E38" t="n">
+        <x:v>10.55</x:v>
+      </x:c>
+      <x:c r="F38" t="n">
+        <x:v>0.5500000000000007</x:v>
+      </x:c>
+      <x:c r="G38" t="n">
+        <x:v>0.05500000000000007</x:v>
+      </x:c>
+      <x:c r="H38" t="n">
+        <x:v>99.13</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L38" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>RPT-2026-237183</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>SGX-VP-2026-0728-G37</x:v>
+      </x:c>
+      <x:c r="O38" t="str">
+        <x:v>BB260725A</x:v>
+      </x:c>
+      <x:c r="P38" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q38" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R38" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S38" t="str">
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T38" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U38" t="str">
+        <x:v>Red</x:v>
+      </x:c>
+      <x:c r="V38" t="str">
+        <x:v>Red flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>COA-0038</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D39" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E39" t="n">
+        <x:v>10.09</x:v>
+      </x:c>
+      <x:c r="F39" t="n">
+        <x:v>0.08999999999999986</x:v>
+      </x:c>
+      <x:c r="G39" t="n">
+        <x:v>0.008999999999999985</x:v>
+      </x:c>
+      <x:c r="H39" t="n">
+        <x:v>99.52</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K39" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L39" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>RPT-2026-442015</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>SGX-VP-2026-0728-K72</x:v>
+      </x:c>
+      <x:c r="O39" t="str">
+        <x:v>TR260725A</x:v>
+      </x:c>
+      <x:c r="P39" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q39" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R39" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S39" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T39" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U39" t="str">
+        <x:v>Yellow</x:v>
+      </x:c>
+      <x:c r="V39" t="str">
+        <x:v>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D40" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E40" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="F40" t="n">
+        <x:v>0.07000000000000028</x:v>
+      </x:c>
+      <x:c r="G40" t="n">
+        <x:v>0.014000000000000058</x:v>
+      </x:c>
+      <x:c r="H40" t="n">
+        <x:v>99.32</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K40" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L40" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>RPT-2026-538821</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>SGX-VP-2026-0728-U17</x:v>
+      </x:c>
+      <x:c r="O40" t="str">
+        <x:v>SM260725A</x:v>
+      </x:c>
+      <x:c r="P40" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q40" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R40" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S40" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T40" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U40" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="V40" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>COA-0040</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="D41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E41" t="n">
+        <x:v>5.13</x:v>
+      </x:c>
+      <x:c r="F41" t="n">
+        <x:v>0.1299999999999999</x:v>
+      </x:c>
+      <x:c r="G41" t="n">
+        <x:v>0.025999999999999978</x:v>
+      </x:c>
+      <x:c r="H41" t="n">
+        <x:v>99.57</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K41" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L41" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M41" t="str">
+        <x:v>RPT-2026-654610</x:v>
+      </x:c>
+      <x:c r="N41" t="str">
+        <x:v>SGX-VP-2026-0728-Z53</x:v>
+      </x:c>
+      <x:c r="O41" t="str">
+        <x:v>BC260725A</x:v>
+      </x:c>
+      <x:c r="P41" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q41" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R41" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S41" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T41" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U41" t="str">
+        <x:v>Green</x:v>
+      </x:c>
+      <x:c r="V41" t="str">
+        <x:v>Green flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>COA-0041</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D42" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E42" t="n">
+        <x:v>51.34</x:v>
+      </x:c>
+      <x:c r="F42" t="n">
+        <x:v>1.3400000000000034</x:v>
+      </x:c>
+      <x:c r="G42" t="n">
+        <x:v>0.026800000000000067</x:v>
+      </x:c>
+      <x:c r="H42" t="n">
+        <x:v>99.78</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K42" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L42" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M42" t="str">
+        <x:v>RPT-2026-697297</x:v>
+      </x:c>
+      <x:c r="N42" t="str">
+        <x:v>SGX-VP-2026-0728-K16</x:v>
+      </x:c>
+      <x:c r="O42" t="str">
+        <x:v>CU260725A</x:v>
+      </x:c>
+      <x:c r="P42" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q42" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R42" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S42" t="str">
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T42" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U42" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="V42" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Ipamorelin</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Growth Hormone Support</x:v>
+      </x:c>
+      <x:c r="D43" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E43" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+      <x:c r="F43" t="n">
+        <x:v>0.16999999999999993</x:v>
+      </x:c>
+      <x:c r="G43" t="n">
+        <x:v>0.03399999999999999</x:v>
+      </x:c>
+      <x:c r="H43" t="n">
+        <x:v>99.34</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K43" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L43" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M43" t="str">
+        <x:v>RPT-2026-822844</x:v>
+      </x:c>
+      <x:c r="N43" t="str">
+        <x:v>SGX-VP-2026-0728-U21</x:v>
+      </x:c>
+      <x:c r="O43" t="str">
+        <x:v>IP260725A</x:v>
+      </x:c>
+      <x:c r="P43" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q43" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R43" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S43" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T43" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U43" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="V43" t="str">
+        <x:v>White flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>COA-0043</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D44" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E44" t="n">
+        <x:v>10.36</x:v>
+      </x:c>
+      <x:c r="F44" t="n">
+        <x:v>0.35999999999999943</x:v>
+      </x:c>
+      <x:c r="G44" t="n">
+        <x:v>0.03599999999999994</x:v>
+      </x:c>
+      <x:c r="H44" t="n">
+        <x:v>99.41</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K44" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L44" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M44" t="str">
+        <x:v>RPT-2026-932680</x:v>
+      </x:c>
+      <x:c r="N44" t="str">
+        <x:v>SGX-VP-2026-0728-G60</x:v>
+      </x:c>
+      <x:c r="O44" t="str">
+        <x:v>RT260725A</x:v>
+      </x:c>
+      <x:c r="P44" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q44" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R44" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S44" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T44" t="str">
+        <x:v>Copper</x:v>
+      </x:c>
+      <x:c r="U44" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="V44" t="str">
+        <x:v>Clear flip-off cap with copper aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>COA-0044</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Amylin / Weight</x:v>
+      </x:c>
+      <x:c r="D45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E45" t="n">
+        <x:v>4.63</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>-0.3700000000000001</x:v>
+      </x:c>
+      <x:c r="G45" t="n">
+        <x:v>-0.07400000000000002</x:v>
+      </x:c>
+      <x:c r="H45" t="n">
+        <x:v>99.67</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>Underfilled</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>Report reviewed</x:v>
+      </x:c>
+      <x:c r="L45" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>Elor5-20260731S0925</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="O45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="P45" t="str">
+        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+      </x:c>
+      <x:c r="Q45" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R45" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S45" t="str">
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+      </x:c>
+      <x:c r="T45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="U45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="V45" t="str">
+        <x:v>Crimp/cap color not listed in the testing record.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14081,7 +16769,7 @@
         <x:v>da424443</x:v>
       </x:c>
       <x:c r="P29" s="14" t="str">
-        <x:v>assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q29" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -14143,7 +16831,7 @@
         <x:v>96ea8238</x:v>
       </x:c>
       <x:c r="P30" s="14" t="str">
-        <x:v>assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q30" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -14205,7 +16893,7 @@
         <x:v>5c1aa528</x:v>
       </x:c>
       <x:c r="P31" s="14" t="str">
-        <x:v>assets/coa/PT-RETA-20-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-RETA-20-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q31" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -14267,7 +16955,7 @@
         <x:v>a8c10db6</x:v>
       </x:c>
       <x:c r="P32" s="14" t="str">
-        <x:v>assets/coa/PT-RETA-30-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-RETA-30-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q32" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -14329,7 +17017,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P33" s="14" t="str">
-        <x:v>assets/coa/photo_2026-07-04_22-14-31.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Semaglutide 15mg)</x:v>
       </x:c>
       <x:c r="Q33" s="14" t="str">
         <x:v>Black</x:v>
@@ -14391,7 +17079,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P34" s="14" t="str">
-        <x:v>assets/coa/photo_2026-07-04_22-34-37.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 30mg)</x:v>
       </x:c>
       <x:c r="Q34" s="14" t="str">
         <x:v>Blue</x:v>
@@ -14453,7 +17141,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P35" s="14" t="str">
-        <x:v>assets/coa/photo_2026-07-04_22-35-21.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 15mg)</x:v>
       </x:c>
       <x:c r="Q35" s="14" t="str">
         <x:v>Purple</x:v>
@@ -14515,7 +17203,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P36" s="14" t="str">
-        <x:v>assets/coa/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
+        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
       </x:c>
       <x:c r="Q36" s="14" t="str">
         <x:v>Clear/Transparent</x:v>
@@ -14577,7 +17265,7 @@
         <x:v>Trio2607170250</x:v>
       </x:c>
       <x:c r="P37" s="14" t="str">
-        <x:v>assets/coa/KLOW80mg-02.pdf</x:v>
+        <x:v>Freedom Diagnostics COA PDF</x:v>
       </x:c>
       <x:c r="Q37" s="14" t="str">
         <x:v>Yellow</x:v>
@@ -14590,6 +17278,502 @@
       </x:c>
       <x:c r="T37" s="14" t="str">
         <x:v>Identity confirmed: GHK-Cu/KPV/BPC-157/Thymosin Beta-4. Net content: GHK-Cu 62.93 mg; KPV 9.09 mg; BPC-157 12.40 mg; Thymosin Beta-4 12.04 mg. Blue lyophilized powder. Received 07/17/2026; reported 07/20/2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>BPC-157 / TB-500 Blend</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Healing / Recovery Blend</x:v>
+      </x:c>
+      <x:c r="D38" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E38" t="n">
+        <x:v>10.55</x:v>
+      </x:c>
+      <x:c r="F38" t="n">
+        <x:v>0.5500000000000007</x:v>
+      </x:c>
+      <x:c r="G38" t="n">
+        <x:v>0.05500000000000007</x:v>
+      </x:c>
+      <x:c r="H38" t="n">
+        <x:v>99.13</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>BB260725A</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L38" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>RPT-2026-237183</x:v>
+      </x:c>
+      <x:c r="O38" t="str">
+        <x:v>SGX-VP-2026-0728-G37</x:v>
+      </x:c>
+      <x:c r="P38" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q38" t="str">
+        <x:v>Red</x:v>
+      </x:c>
+      <x:c r="R38" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="S38" t="str">
+        <x:v>Red flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T38" t="str">
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>COA-0038</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D39" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E39" t="n">
+        <x:v>10.09</x:v>
+      </x:c>
+      <x:c r="F39" t="n">
+        <x:v>0.08999999999999986</x:v>
+      </x:c>
+      <x:c r="G39" t="n">
+        <x:v>0.008999999999999985</x:v>
+      </x:c>
+      <x:c r="H39" t="n">
+        <x:v>99.52</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>TR260725A</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K39" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="L39" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>COA-0038</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>RPT-2026-442015</x:v>
+      </x:c>
+      <x:c r="O39" t="str">
+        <x:v>SGX-VP-2026-0728-K72</x:v>
+      </x:c>
+      <x:c r="P39" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q39" t="str">
+        <x:v>Yellow</x:v>
+      </x:c>
+      <x:c r="R39" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="S39" t="str">
+        <x:v>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T39" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D40" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E40" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="F40" t="n">
+        <x:v>0.07000000000000028</x:v>
+      </x:c>
+      <x:c r="G40" t="n">
+        <x:v>0.014000000000000058</x:v>
+      </x:c>
+      <x:c r="H40" t="n">
+        <x:v>99.32</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>SM260725A</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K40" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="L40" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>RPT-2026-538821</x:v>
+      </x:c>
+      <x:c r="O40" t="str">
+        <x:v>SGX-VP-2026-0728-U17</x:v>
+      </x:c>
+      <x:c r="P40" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q40" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="R40" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="S40" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T40" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>COA-0040</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="D41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E41" t="n">
+        <x:v>5.13</x:v>
+      </x:c>
+      <x:c r="F41" t="n">
+        <x:v>0.1299999999999999</x:v>
+      </x:c>
+      <x:c r="G41" t="n">
+        <x:v>0.025999999999999978</x:v>
+      </x:c>
+      <x:c r="H41" t="n">
+        <x:v>99.57</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>BC260725A</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K41" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L41" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M41" t="str">
+        <x:v>COA-0040</x:v>
+      </x:c>
+      <x:c r="N41" t="str">
+        <x:v>RPT-2026-654610</x:v>
+      </x:c>
+      <x:c r="O41" t="str">
+        <x:v>SGX-VP-2026-0728-Z53</x:v>
+      </x:c>
+      <x:c r="P41" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q41" t="str">
+        <x:v>Green</x:v>
+      </x:c>
+      <x:c r="R41" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="S41" t="str">
+        <x:v>Green flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T41" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>COA-0041</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D42" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E42" t="n">
+        <x:v>51.34</x:v>
+      </x:c>
+      <x:c r="F42" t="n">
+        <x:v>1.3400000000000034</x:v>
+      </x:c>
+      <x:c r="G42" t="n">
+        <x:v>0.026800000000000067</x:v>
+      </x:c>
+      <x:c r="H42" t="n">
+        <x:v>99.78</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>CU260725A</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K42" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L42" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M42" t="str">
+        <x:v>COA-0041</x:v>
+      </x:c>
+      <x:c r="N42" t="str">
+        <x:v>RPT-2026-697297</x:v>
+      </x:c>
+      <x:c r="O42" t="str">
+        <x:v>SGX-VP-2026-0728-K16</x:v>
+      </x:c>
+      <x:c r="P42" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q42" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="R42" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="S42" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T42" t="str">
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Ipamorelin</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Growth Hormone Support</x:v>
+      </x:c>
+      <x:c r="D43" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E43" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+      <x:c r="F43" t="n">
+        <x:v>0.16999999999999993</x:v>
+      </x:c>
+      <x:c r="G43" t="n">
+        <x:v>0.03399999999999999</x:v>
+      </x:c>
+      <x:c r="H43" t="n">
+        <x:v>99.34</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>IP260725A</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K43" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L43" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M43" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+      <x:c r="N43" t="str">
+        <x:v>RPT-2026-822844</x:v>
+      </x:c>
+      <x:c r="O43" t="str">
+        <x:v>SGX-VP-2026-0728-U21</x:v>
+      </x:c>
+      <x:c r="P43" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q43" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="R43" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="S43" t="str">
+        <x:v>White flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T43" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>COA-0043</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D44" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E44" t="n">
+        <x:v>10.36</x:v>
+      </x:c>
+      <x:c r="F44" t="n">
+        <x:v>0.35999999999999943</x:v>
+      </x:c>
+      <x:c r="G44" t="n">
+        <x:v>0.03599999999999994</x:v>
+      </x:c>
+      <x:c r="H44" t="n">
+        <x:v>99.41</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>RT260725A</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K44" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L44" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M44" t="str">
+        <x:v>COA-0043</x:v>
+      </x:c>
+      <x:c r="N44" t="str">
+        <x:v>RPT-2026-932680</x:v>
+      </x:c>
+      <x:c r="O44" t="str">
+        <x:v>SGX-VP-2026-0728-G60</x:v>
+      </x:c>
+      <x:c r="P44" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q44" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="R44" t="str">
+        <x:v>Copper</x:v>
+      </x:c>
+      <x:c r="S44" t="str">
+        <x:v>Clear flip-off cap with copper aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T44" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>COA-0044</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Amylin / Weight</x:v>
+      </x:c>
+      <x:c r="D45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E45" t="n">
+        <x:v>4.63</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>-0.3700000000000001</x:v>
+      </x:c>
+      <x:c r="G45" t="n">
+        <x:v>-0.07400000000000002</x:v>
+      </x:c>
+      <x:c r="H45" t="n">
+        <x:v>99.67</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>Underfilled</x:v>
+      </x:c>
+      <x:c r="L45" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>COA-0044</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>Elor5-20260731S0925</x:v>
+      </x:c>
+      <x:c r="O45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="P45" t="str">
+        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+      </x:c>
+      <x:c r="Q45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="R45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="S45" t="str">
+        <x:v>Crimp/cap color not listed in the testing record.</x:v>
+      </x:c>
+      <x:c r="T45" t="str">
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16448,7 +19632,7 @@
         <x:v>da424443</x:v>
       </x:c>
       <x:c r="G29" s="14" t="str">
-        <x:v>assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H29" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16513,7 +19697,7 @@
         <x:v>96ea8238</x:v>
       </x:c>
       <x:c r="G30" s="14" t="str">
-        <x:v>assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H30" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16578,7 +19762,7 @@
         <x:v>5c1aa528</x:v>
       </x:c>
       <x:c r="G31" s="14" t="str">
-        <x:v>assets/coa/PT-RETA-20-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-RETA-20-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H31" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16643,7 +19827,7 @@
         <x:v>a8c10db6</x:v>
       </x:c>
       <x:c r="G32" s="14" t="str">
-        <x:v>assets/coa/PT-RETA-30-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-RETA-30-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H32" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16708,7 +19892,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="G33" s="14" t="str">
-        <x:v>assets/coa/photo_2026-07-04_22-14-31.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Semaglutide 15mg)</x:v>
       </x:c>
       <x:c r="H33" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16773,7 +19957,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="G34" s="14" t="str">
-        <x:v>assets/coa/photo_2026-07-04_22-34-37.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 30mg)</x:v>
       </x:c>
       <x:c r="H34" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16838,7 +20022,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="G35" s="14" t="str">
-        <x:v>assets/coa/photo_2026-07-04_22-35-21.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 15mg)</x:v>
       </x:c>
       <x:c r="H35" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16903,7 +20087,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="G36" s="14" t="str">
-        <x:v>assets/coa/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
+        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
       </x:c>
       <x:c r="H36" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16968,7 +20152,7 @@
         <x:v>Trio2607170250</x:v>
       </x:c>
       <x:c r="G37" s="14" t="str">
-        <x:v>assets/coa/KLOW80mg-02.pdf</x:v>
+        <x:v>Freedom Diagnostics COA PDF</x:v>
       </x:c>
       <x:c r="H37" s="14" t="str">
         <x:v>Yes</x:v>
@@ -17011,6 +20195,526 @@
       </x:c>
       <x:c r="U37" s="14" t="str">
         <x:v>Yellow flip-off cap with silver aluminum crimp, based on the vial image shown on page 1 of the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>BPC-157 / TB-500 Blend</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Healing / Recovery Blend</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>RPT-2026-237183</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>SGX-VP-2026-0728-G37</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I38" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J38" t="n">
+        <x:v>10.55</x:v>
+      </x:c>
+      <x:c r="K38" t="n">
+        <x:v>0.5500000000000007</x:v>
+      </x:c>
+      <x:c r="L38" t="n">
+        <x:v>0.05500000000000007</x:v>
+      </x:c>
+      <x:c r="M38" t="n">
+        <x:v>99.13</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O38" t="str">
+        <x:v>BB260725A</x:v>
+      </x:c>
+      <x:c r="P38" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="Q38" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R38" t="str">
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="S38" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="T38" t="str">
+        <x:v>Red</x:v>
+      </x:c>
+      <x:c r="U38" t="str">
+        <x:v>Red flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>COA-0038</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>RPT-2026-442015</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>SGX-VP-2026-0728-K72</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I39" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J39" t="n">
+        <x:v>10.09</x:v>
+      </x:c>
+      <x:c r="K39" t="n">
+        <x:v>0.08999999999999986</x:v>
+      </x:c>
+      <x:c r="L39" t="n">
+        <x:v>0.008999999999999985</x:v>
+      </x:c>
+      <x:c r="M39" t="n">
+        <x:v>99.52</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="O39" t="str">
+        <x:v>TR260725A</x:v>
+      </x:c>
+      <x:c r="P39" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="Q39" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R39" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="S39" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="T39" t="str">
+        <x:v>Yellow</x:v>
+      </x:c>
+      <x:c r="U39" t="str">
+        <x:v>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>RPT-2026-538821</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>SGX-VP-2026-0728-U17</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I40" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J40" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="K40" t="n">
+        <x:v>0.07000000000000028</x:v>
+      </x:c>
+      <x:c r="L40" t="n">
+        <x:v>0.014000000000000058</x:v>
+      </x:c>
+      <x:c r="M40" t="n">
+        <x:v>99.32</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="O40" t="str">
+        <x:v>SM260725A</x:v>
+      </x:c>
+      <x:c r="P40" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="Q40" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R40" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="S40" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="T40" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="U40" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>COA-0040</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>RPT-2026-654610</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>SGX-VP-2026-0728-Z53</x:v>
+      </x:c>
+      <x:c r="G41" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J41" t="n">
+        <x:v>5.13</x:v>
+      </x:c>
+      <x:c r="K41" t="n">
+        <x:v>0.1299999999999999</x:v>
+      </x:c>
+      <x:c r="L41" t="n">
+        <x:v>0.025999999999999978</x:v>
+      </x:c>
+      <x:c r="M41" t="n">
+        <x:v>99.57</x:v>
+      </x:c>
+      <x:c r="N41" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O41" t="str">
+        <x:v>BC260725A</x:v>
+      </x:c>
+      <x:c r="P41" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="Q41" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R41" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="S41" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="T41" t="str">
+        <x:v>Green</x:v>
+      </x:c>
+      <x:c r="U41" t="str">
+        <x:v>Green flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>COA-0041</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>RPT-2026-697297</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>SGX-VP-2026-0728-K16</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I42" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J42" t="n">
+        <x:v>51.34</x:v>
+      </x:c>
+      <x:c r="K42" t="n">
+        <x:v>1.3400000000000034</x:v>
+      </x:c>
+      <x:c r="L42" t="n">
+        <x:v>0.026800000000000067</x:v>
+      </x:c>
+      <x:c r="M42" t="n">
+        <x:v>99.78</x:v>
+      </x:c>
+      <x:c r="N42" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O42" t="str">
+        <x:v>CU260725A</x:v>
+      </x:c>
+      <x:c r="P42" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="Q42" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R42" t="str">
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="S42" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="T42" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="U42" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Ipamorelin</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Growth Hormone Support</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>RPT-2026-822844</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>SGX-VP-2026-0728-U21</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I43" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J43" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+      <x:c r="K43" t="n">
+        <x:v>0.16999999999999993</x:v>
+      </x:c>
+      <x:c r="L43" t="n">
+        <x:v>0.03399999999999999</x:v>
+      </x:c>
+      <x:c r="M43" t="n">
+        <x:v>99.34</x:v>
+      </x:c>
+      <x:c r="N43" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O43" t="str">
+        <x:v>IP260725A</x:v>
+      </x:c>
+      <x:c r="P43" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="Q43" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R43" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="S43" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="T43" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="U43" t="str">
+        <x:v>White flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>COA-0043</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>RPT-2026-932680</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>SGX-VP-2026-0728-G60</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I44" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J44" t="n">
+        <x:v>10.36</x:v>
+      </x:c>
+      <x:c r="K44" t="n">
+        <x:v>0.35999999999999943</x:v>
+      </x:c>
+      <x:c r="L44" t="n">
+        <x:v>0.03599999999999994</x:v>
+      </x:c>
+      <x:c r="M44" t="n">
+        <x:v>99.41</x:v>
+      </x:c>
+      <x:c r="N44" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O44" t="str">
+        <x:v>RT260725A</x:v>
+      </x:c>
+      <x:c r="P44" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="Q44" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R44" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="S44" t="str">
+        <x:v>Copper</x:v>
+      </x:c>
+      <x:c r="T44" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="U44" t="str">
+        <x:v>Clear flip-off cap with copper aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>COA-0044</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Amylin / Weight</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>Elor5-20260731S0925</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J45" t="n">
+        <x:v>4.63</x:v>
+      </x:c>
+      <x:c r="K45" t="n">
+        <x:v>-0.3700000000000001</x:v>
+      </x:c>
+      <x:c r="L45" t="n">
+        <x:v>-0.07400000000000002</x:v>
+      </x:c>
+      <x:c r="M45" t="n">
+        <x:v>99.67</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>Underfilled</x:v>
+      </x:c>
+      <x:c r="O45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="P45" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="Q45" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R45" t="str">
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+      </x:c>
+      <x:c r="S45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="T45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="U45" t="str">
+        <x:v>Crimp/cap color not listed in the testing record.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -17052,63 +20756,67 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
-        <x:v>AOD-9604</x:v>
+        <x:v>ADAMAX</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
         <x:v>Aminos Analytics</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>Review</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>Clear Green</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Copper</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Amylin / Weight</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="str">
-        <x:v>BPC-157</x:v>
+        <x:v>AOD-9604</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
         <x:v>BT Labs</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
-        <x:v>Gold</x:v>
-      </x:c>
-      <x:c r="E3" s="14"/>
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
       <x:c r="F3" s="14" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>Cosmetic / Recovery</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str">
-        <x:v>CJC-1295 No DAC</x:v>
+        <x:v>BPC-157</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
         <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>Review</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
-        <x:v>Gray</x:v>
-      </x:c>
-      <x:c r="E4" s="14"/>
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
       <x:c r="F4" s="14" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>BPC-157 / TB-500 Blend</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
         <x:v>Janoshik</x:v>
@@ -17117,80 +20825,104 @@
         <x:v>Underfilled</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Clear Green</x:v>
       </x:c>
       <x:c r="E5" s="14"/>
       <x:c r="F5" s="14" t="str">
-        <x:v>Metabolic / Fat Loss</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
-        <x:v>KPV</x:v>
+        <x:v>BPC/TB Blend</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="C6" s="14"/>
       <x:c r="D6" s="14" t="str">
-        <x:v>Royal Blue</x:v>
+        <x:v>Clear/Transparent</x:v>
       </x:c>
       <x:c r="E6" s="14"/>
       <x:c r="F6" s="14" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
-        <x:v>MOTS-C</x:v>
-      </x:c>
-      <x:c r="B7" s="14"/>
+        <x:v>CJC-1295 No DAC</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
       <x:c r="C7" s="14"/>
-      <x:c r="D7" s="14"/>
+      <x:c r="D7" s="14" t="str">
+        <x:v>Gold</x:v>
+      </x:c>
       <x:c r="E7" s="14"/>
       <x:c r="F7" s="14" t="str">
-        <x:v>Other</x:v>
+        <x:v>Healing / Recovery Blend</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
-        <x:v>Retatrutide</x:v>
-      </x:c>
-      <x:c r="B8" s="14"/>
+        <x:v>Cagrilintide</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>Testides</x:v>
+      </x:c>
       <x:c r="C8" s="14"/>
-      <x:c r="D8" s="14"/>
+      <x:c r="D8" s="14" t="str">
+        <x:v>Gray</x:v>
+      </x:c>
       <x:c r="E8" s="14"/>
-      <x:c r="F8" s="14"/>
+      <x:c r="F8" s="14" t="str">
+        <x:v>Metabolic / Fat Loss</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
-        <x:v>SS-31</x:v>
-      </x:c>
-      <x:c r="B9" s="14"/>
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
       <x:c r="C9" s="14"/>
-      <x:c r="D9" s="14"/>
+      <x:c r="D9" s="14" t="str">
+        <x:v>Green</x:v>
+      </x:c>
       <x:c r="E9" s="14"/>
-      <x:c r="F9" s="14"/>
+      <x:c r="F9" s="14" t="str">
+        <x:v>Metabolic / Mito</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="B10" s="14"/>
       <x:c r="C10" s="14"/>
-      <x:c r="D10" s="14"/>
+      <x:c r="D10" s="14" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
       <x:c r="E10" s="14"/>
-      <x:c r="F10" s="14"/>
+      <x:c r="F10" s="14" t="str">
+        <x:v>Other</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Ipamorelin</x:v>
       </x:c>
       <x:c r="B11" s="14"/>
       <x:c r="C11" s="14"/>
-      <x:c r="D11" s="14"/>
+      <x:c r="D11" s="14" t="str">
+        <x:v>Purple</x:v>
+      </x:c>
       <x:c r="E11" s="14"/>
-      <x:c r="F11" s="14"/>
+      <x:c r="F11" s="14" t="str">
+        <x:v>Regenerative / Skin</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="str">
@@ -17198,39 +20930,91 @@
       </x:c>
       <x:c r="B12" s="14"/>
       <x:c r="C12" s="14"/>
-      <x:c r="D12" s="14"/>
+      <x:c r="D12" s="14" t="str">
+        <x:v>Red</x:v>
+      </x:c>
       <x:c r="E12" s="14"/>
-      <x:c r="F12" s="14"/>
+      <x:c r="F12" s="14" t="str">
+        <x:v>Research Peptide</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="14"/>
+      <x:c r="A13" s="14" t="str">
+        <x:v>KPV</x:v>
+      </x:c>
       <x:c r="B13" s="14"/>
       <x:c r="C13" s="14"/>
       <x:c r="D13" s="14" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Royal Blue</x:v>
       </x:c>
       <x:c r="E13" s="14"/>
       <x:c r="F13" s="14"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="14"/>
+      <x:c r="A14" s="14" t="str">
+        <x:v>MOTS-C</x:v>
+      </x:c>
       <x:c r="B14" s="14"/>
       <x:c r="C14" s="14"/>
-      <x:c r="D14" s="14"/>
-      <x:c r="E14" s="14" t="str">
-        <x:v>Silver</x:v>
-      </x:c>
+      <x:c r="D14" s="14" t="str">
+        <x:v>Transparent</x:v>
+      </x:c>
+      <x:c r="E14" s="14"/>
       <x:c r="F14" s="14"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="14"/>
+      <x:c r="A15" s="14" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
       <x:c r="B15" s="14"/>
       <x:c r="C15" s="14"/>
-      <x:c r="D15" s="14"/>
+      <x:c r="D15" s="14" t="str">
+        <x:v>White</x:v>
+      </x:c>
       <x:c r="E15" s="14"/>
-      <x:c r="F15" s="14" t="str">
-        <x:v>Healing / Recovery Blend</x:v>
-      </x:c>
+      <x:c r="F15" s="14"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>SS-31</x:v>
+      </x:c>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16" t="str">
+        <x:v>Yellow</x:v>
+      </x:c>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>TB-500</x:v>
+      </x:c>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/inventory_updated.xlsx
+++ b/inventory_updated.xlsx
@@ -2,29 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbbf8fff600fa4d6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R3b78202dc6a74ae5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R6fc2db3548414f01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R97da5e87ee3e4b0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R9b7a4f4d30874686"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="R4c79e0b8ac2145e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="Rd217690a545542c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Raaa96cd61291447f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="Rc5187fbaeab140b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="Rf2f7610cb59348a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="Reb2df176e9ba4a8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Rb1515e023dc44e20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R3d22b3c1193646a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="Rf5e741a1ac4b4ee9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R09ba65a46f1a451c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="Rf14273d99b9a45be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="R4f01d343e87a4100"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="R5a5a8e506bc047e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="Rc266f040c8574520"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="Rb630cf48e01e4bf3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R189b65b697ef4cae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R39f494d027354ce4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="Ra49c5376f63a4ace"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R45d5d17dfc064468"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="Rda10b86a89084036"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R934d8326b2474c8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R887d038d4bc54770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R255073150b574187"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="R3eff75215aaa43cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="Reef50f4fc6f24ba0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="R84af0ff6ca6f45f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R5e997037b2c246fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="R75319b4132734f95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="R3080bec47b574cc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="R68074d6c70fc443e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="Rbef1ec3c66904d39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="R2961d3a3e4664ac0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R137bd21b37974d51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="R708aa0da2db04ed2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="R26b00ea1bb364f58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="Re445112bbe0c402c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="R3464b71789ca4680"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="Re90d5bc4dd7d4951"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R1185ab21f5fe48db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R6740b4887e0e4858"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="R61068cddb0184a15"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/inventory_updated.xlsx
+++ b/inventory_updated.xlsx
@@ -2,29 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R45d5d17dfc064468"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="Rda10b86a89084036"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R934d8326b2474c8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R887d038d4bc54770"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R255073150b574187"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="R3eff75215aaa43cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="Reef50f4fc6f24ba0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="R84af0ff6ca6f45f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R5e997037b2c246fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="R75319b4132734f95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="R3080bec47b574cc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="R68074d6c70fc443e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="Rbef1ec3c66904d39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="R2961d3a3e4664ac0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R137bd21b37974d51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="R708aa0da2db04ed2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="R26b00ea1bb364f58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="Re445112bbe0c402c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="R3464b71789ca4680"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="Re90d5bc4dd7d4951"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R1185ab21f5fe48db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R6740b4887e0e4858"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="R61068cddb0184a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbbf8fff600fa4d6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R3b78202dc6a74ae5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R6fc2db3548414f01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R97da5e87ee3e4b0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R9b7a4f4d30874686"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="R4c79e0b8ac2145e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="Rd217690a545542c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Raaa96cd61291447f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="Rc5187fbaeab140b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="Rf2f7610cb59348a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="Reb2df176e9ba4a8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Rb1515e023dc44e20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R3d22b3c1193646a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="Rf5e741a1ac4b4ee9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R09ba65a46f1a451c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="Rf14273d99b9a45be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="R4f01d343e87a4100"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="R5a5a8e506bc047e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="Rc266f040c8574520"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="Rb630cf48e01e4bf3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R189b65b697ef4cae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R39f494d027354ce4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="Ra49c5376f63a4ace"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/inventory_updated.xlsx
+++ b/inventory_updated.xlsx
@@ -2,29 +2,31 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbbf8fff600fa4d6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R3b78202dc6a74ae5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R6fc2db3548414f01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R97da5e87ee3e4b0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R9b7a4f4d30874686"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="R4c79e0b8ac2145e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="Rd217690a545542c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Raaa96cd61291447f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="Rc5187fbaeab140b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="Rf2f7610cb59348a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="Reb2df176e9ba4a8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Rb1515e023dc44e20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R3d22b3c1193646a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="Rf5e741a1ac4b4ee9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R09ba65a46f1a451c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="Rf14273d99b9a45be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="R4f01d343e87a4100"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="R5a5a8e506bc047e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="Rc266f040c8574520"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="Rb630cf48e01e4bf3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R189b65b697ef4cae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R39f494d027354ce4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="Ra49c5376f63a4ace"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Raaa0019301a84776"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R14d526503f7a45ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="Rdfd0a6810ff645b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R8b84b8d795e244f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="Rb27ceb38d0614c97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="R78cb254836614d79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R7adda934d93240c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="R13d94284d7564349"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="Re3ecbc6056c94ded"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="Re3d8ab8930ec4017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="Redad29ae569a4a08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Rb6b01744778847c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="Raf1dd614fa3540a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="Ra4ca487016184d8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="Rb4afbbcf407c4922"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="R5676b4f5abf34796"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="Rc2144880c42c4765"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="R2c06667615e0476a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="R56e696e23ab2444b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="R9b7ec54561ef4158"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R7e928ef02d77473a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R3764fe13e4cf4d39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="R419f03db7be947f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0045" sheetId="24" r:id="R1f95ffdd690b4388"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0046" sheetId="25" r:id="R59180bfe69d54410"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -39,7 +41,7 @@
     <x:numFmt numFmtId="200" formatCode="0.00%"/>
     <x:numFmt numFmtId="201" formatCode="0.000"/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -48,6 +50,11 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -71,7 +78,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -119,6 +126,11 @@
     </x:xf>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -170,9 +182,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -310,7 +322,7 @@
         <x:v>Total COA Records</x:v>
       </x:c>
       <x:c r="B3" s="14" t="n">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
         <x:v>Synced from COA Database</x:v>
@@ -323,10 +335,10 @@
         <x:v>Unique Peptides</x:v>
       </x:c>
       <x:c r="B4" s="14" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, Eloralintide, GHK-Cu, Ipamorelin, KLOW 80mg, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
+        <x:v>ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295, CJC-1295 No DAC, Cagrilintide, Eloralintide, GHK-Cu, Ipamorelin, KLOW 80mg, KPV, MOTS-C, NAD+, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
       </x:c>
       <x:c r="D4" s="14"/>
       <x:c r="E4" s="14"/>
@@ -336,7 +348,7 @@
         <x:v>Average Purity %</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:v>99.613</x:v>
+        <x:v>99.614</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
         <x:v>Populated purity results</x:v>
@@ -349,7 +361,7 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="14"/>
       <x:c r="D6" s="14"/>
@@ -371,7 +383,7 @@
         <x:v>On Label/Review</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C8" s="14"/>
       <x:c r="D8" s="14"/>
@@ -382,10 +394,10 @@
         <x:v>Labs Used</x:v>
       </x:c>
       <x:c r="B9" s="14" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>Aminos Analytics, BT Labs, Freedom Diagnostics, Janoshik, Kovera Labs, SteriGenix, Testides, Tianjin Qiangxin (third-party partner lab)</x:v>
+        <x:v>Aminos Analytics, BT Labs, Freedom Diagnostics, ILS Laboratories, Janoshik, Kovera Labs, SteriGenix, Testides, Tianjin Qiangxin (third-party partner lab)</x:v>
       </x:c>
       <x:c r="D9" s="14"/>
       <x:c r="E9" s="14"/>
@@ -546,16 +558,16 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="14" t="str">
-        <x:v>COA-0044</x:v>
+        <x:v>COA-0045</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>Eloralintide</x:v>
+        <x:v>CJC-1295</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+        <x:v>ILS Laboratories</x:v>
       </x:c>
       <x:c r="D20" s="14" t="n">
-        <x:v>99.67</x:v>
+        <x:v>99.72</x:v>
       </x:c>
       <x:c r="E20" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -563,16 +575,16 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="14" t="str">
-        <x:v>COA-0004</x:v>
+        <x:v>COA-0044</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Eloralintide</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
       </x:c>
       <x:c r="D21" s="14" t="n">
-        <x:v>99.491</x:v>
+        <x:v>99.67</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -580,33 +592,33 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="14" t="str">
-        <x:v>COA-0003</x:v>
+        <x:v>COA-0046</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>NAD+</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="D22" s="14" t="n">
-        <x:v>99.654</x:v>
+        <x:v>99.549</x:v>
       </x:c>
       <x:c r="E22" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Black</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="14" t="str">
-        <x:v>COA-0023</x:v>
+        <x:v>COA-0004</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="D23" s="14" t="n">
-        <x:v>99.731</x:v>
+        <x:v>99.491</x:v>
       </x:c>
       <x:c r="E23" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -614,16 +626,16 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="14" t="str">
-        <x:v>COA-0022</x:v>
+        <x:v>COA-0003</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
         <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="D24" s="14" t="n">
-        <x:v>99.825</x:v>
+        <x:v>99.654</x:v>
       </x:c>
       <x:c r="E24" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -631,16 +643,16 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="14" t="str">
-        <x:v>COA-0021</x:v>
+        <x:v>COA-0023</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>CJC-1295 No DAC</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D25" s="14" t="n">
-        <x:v>99.897</x:v>
+        <x:v>99.731</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -648,16 +660,16 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="14" t="str">
-        <x:v>COA-0012</x:v>
+        <x:v>COA-0022</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>AOD-9604</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D26" s="14" t="n">
-        <x:v>99.883</x:v>
+        <x:v>99.825</x:v>
       </x:c>
       <x:c r="E26" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -665,16 +677,16 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="14" t="str">
-        <x:v>COA-0001</x:v>
+        <x:v>COA-0021</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>CJC-1295 No DAC</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D27" s="14" t="n">
-        <x:v>99.516</x:v>
+        <x:v>99.897</x:v>
       </x:c>
       <x:c r="E27" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -682,16 +694,16 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="14" t="str">
-        <x:v>COA-0019</x:v>
+        <x:v>COA-0012</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
-        <x:v>SS-31</x:v>
+        <x:v>AOD-9604</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D28" s="14" t="n">
-        <x:v>99.95</x:v>
+        <x:v>99.883</x:v>
       </x:c>
       <x:c r="E28" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -699,16 +711,16 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="14" t="str">
-        <x:v>COA-0016</x:v>
+        <x:v>COA-0001</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D29" s="14" t="n">
-        <x:v>99.085</x:v>
+        <x:v>99.516</x:v>
       </x:c>
       <x:c r="E29" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -716,16 +728,16 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="14" t="str">
-        <x:v>COA-0014</x:v>
+        <x:v>COA-0019</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>SS-31</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D30" s="14" t="n">
-        <x:v>99.055</x:v>
+        <x:v>99.95</x:v>
       </x:c>
       <x:c r="E30" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -733,16 +745,16 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="14" t="str">
-        <x:v>COA-0011</x:v>
+        <x:v>COA-0016</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>TB-500</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D31" s="14" t="n">
-        <x:v>99.04</x:v>
+        <x:v>99.085</x:v>
       </x:c>
       <x:c r="E31" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -750,16 +762,16 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="14" t="str">
-        <x:v>COA-0006</x:v>
+        <x:v>COA-0014</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>Aminos Analytics</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D32" s="14" t="n">
-        <x:v>99.5</x:v>
+        <x:v>99.055</x:v>
       </x:c>
       <x:c r="E32" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -857,7 +869,7 @@
         <x:v>Total COA/Test Records</x:v>
       </x:c>
       <x:c r="B3" s="14" t="n">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
         <x:v>All records from COA Database</x:v>
@@ -884,10 +896,10 @@
         <x:v>Unique Peptides</x:v>
       </x:c>
       <x:c r="B4" s="14" t="n">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>ADAMAX, AOD-9604, BPC-157, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, GHK-Cu, KLOW 80mg, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
+        <x:v>ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295, CJC-1295 No DAC, Cagrilintide, Eloralintide, GHK-Cu, Ipamorelin, KLOW 80mg, KPV, MOTS-C, NAD+, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
       </x:c>
       <x:c r="D4" s="14"/>
       <x:c r="E4" s="14"/>
@@ -911,7 +923,7 @@
         <x:v>Passed Records</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
         <x:v>Pass/Fail column</x:v>
@@ -938,7 +950,7 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
         <x:v>Status column</x:v>
@@ -965,7 +977,7 @@
         <x:v>Underfilled</x:v>
       </x:c>
       <x:c r="B7" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
         <x:v>Status column</x:v>
@@ -992,7 +1004,7 @@
         <x:v>On Label/Review</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
         <x:v>Status column</x:v>
@@ -1019,7 +1031,7 @@
         <x:v>Average Purity %</x:v>
       </x:c>
       <x:c r="B9" s="14" t="n">
-        <x:v>99.613</x:v>
+        <x:v>99.614</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
         <x:v>Based on populated purity values</x:v>
@@ -1046,10 +1058,10 @@
         <x:v>Unique Labs</x:v>
       </x:c>
       <x:c r="B10" s="14" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
-        <x:v>Aminos Analytics, BT Labs, Freedom Diagnostics, Janoshik, Kovera Labs, SteriGenix, Testides</x:v>
+        <x:v>Aminos Analytics, BT Labs, Freedom Diagnostics, ILS Laboratories, Janoshik, Kovera Labs, SteriGenix, Testides, Tianjin Qiangxin (third-party partner lab)</x:v>
       </x:c>
       <x:c r="D10" s="14"/>
       <x:c r="E10" s="14"/>
@@ -1073,7 +1085,7 @@
         <x:v>Last Test Date</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
         <x:v>Most recent test date</x:v>
@@ -3281,6 +3293,596 @@
       </x:c>
       <x:c r="S49" s="14" t="str">
         <x:v>Identity confirmed: GHK-Cu/KPV/BPC-157/Thymosin Beta-4. Net content: GHK-Cu 62.93 mg; KPV 9.09 mg; BPC-157 12.40 mg; Thymosin Beta-4 12.04 mg. Blue lyophilized powder. Received 07/17/2026; reported 07/20/2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>BPC-157 / TB-500 Blend</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>Healing / Recovery Blend</x:v>
+      </x:c>
+      <x:c r="D50" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E50" t="n">
+        <x:v>10.55</x:v>
+      </x:c>
+      <x:c r="F50" t="n">
+        <x:v>0.5500000000000007</x:v>
+      </x:c>
+      <x:c r="G50" t="n">
+        <x:v>0.05500000000000007</x:v>
+      </x:c>
+      <x:c r="H50" t="n">
+        <x:v>99.13</x:v>
+      </x:c>
+      <x:c r="I50" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J50" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K50" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L50" t="str">
+        <x:v>RPT-2026-237183</x:v>
+      </x:c>
+      <x:c r="M50" t="str">
+        <x:v>SGX-VP-2026-0728-G37</x:v>
+      </x:c>
+      <x:c r="N50" t="str">
+        <x:v>BB260725A</x:v>
+      </x:c>
+      <x:c r="O50" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P50" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="Q50" t="str">
+        <x:v>Red</x:v>
+      </x:c>
+      <x:c r="R50" t="str">
+        <x:v>Red flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S50" t="str">
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>COA-0038</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D51" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E51" t="n">
+        <x:v>10.09</x:v>
+      </x:c>
+      <x:c r="F51" t="n">
+        <x:v>0.08999999999999986</x:v>
+      </x:c>
+      <x:c r="G51" t="n">
+        <x:v>0.008999999999999985</x:v>
+      </x:c>
+      <x:c r="H51" t="n">
+        <x:v>99.52</x:v>
+      </x:c>
+      <x:c r="I51" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J51" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K51" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L51" t="str">
+        <x:v>RPT-2026-442015</x:v>
+      </x:c>
+      <x:c r="M51" t="str">
+        <x:v>SGX-VP-2026-0728-K72</x:v>
+      </x:c>
+      <x:c r="N51" t="str">
+        <x:v>TR260725A</x:v>
+      </x:c>
+      <x:c r="O51" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P51" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="Q51" t="str">
+        <x:v>Yellow</x:v>
+      </x:c>
+      <x:c r="R51" t="str">
+        <x:v>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S51" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D52" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E52" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="F52" t="n">
+        <x:v>0.07000000000000028</x:v>
+      </x:c>
+      <x:c r="G52" t="n">
+        <x:v>0.014000000000000058</x:v>
+      </x:c>
+      <x:c r="H52" t="n">
+        <x:v>99.32</x:v>
+      </x:c>
+      <x:c r="I52" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J52" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K52" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L52" t="str">
+        <x:v>RPT-2026-538821</x:v>
+      </x:c>
+      <x:c r="M52" t="str">
+        <x:v>SGX-VP-2026-0728-U17</x:v>
+      </x:c>
+      <x:c r="N52" t="str">
+        <x:v>SM260725A</x:v>
+      </x:c>
+      <x:c r="O52" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P52" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="Q52" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="R52" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S52" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="str">
+        <x:v>COA-0040</x:v>
+      </x:c>
+      <x:c r="B53" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="D53" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E53" t="n">
+        <x:v>5.13</x:v>
+      </x:c>
+      <x:c r="F53" t="n">
+        <x:v>0.1299999999999999</x:v>
+      </x:c>
+      <x:c r="G53" t="n">
+        <x:v>0.025999999999999978</x:v>
+      </x:c>
+      <x:c r="H53" t="n">
+        <x:v>99.57</x:v>
+      </x:c>
+      <x:c r="I53" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J53" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K53" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L53" t="str">
+        <x:v>RPT-2026-654610</x:v>
+      </x:c>
+      <x:c r="M53" t="str">
+        <x:v>SGX-VP-2026-0728-Z53</x:v>
+      </x:c>
+      <x:c r="N53" t="str">
+        <x:v>BC260725A</x:v>
+      </x:c>
+      <x:c r="O53" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P53" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="Q53" t="str">
+        <x:v>Green</x:v>
+      </x:c>
+      <x:c r="R53" t="str">
+        <x:v>Green flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S53" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str">
+        <x:v>COA-0041</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D54" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E54" t="n">
+        <x:v>51.34</x:v>
+      </x:c>
+      <x:c r="F54" t="n">
+        <x:v>1.3400000000000034</x:v>
+      </x:c>
+      <x:c r="G54" t="n">
+        <x:v>0.026800000000000067</x:v>
+      </x:c>
+      <x:c r="H54" t="n">
+        <x:v>99.78</x:v>
+      </x:c>
+      <x:c r="I54" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J54" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K54" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L54" t="str">
+        <x:v>RPT-2026-697297</x:v>
+      </x:c>
+      <x:c r="M54" t="str">
+        <x:v>SGX-VP-2026-0728-K16</x:v>
+      </x:c>
+      <x:c r="N54" t="str">
+        <x:v>CU260725A</x:v>
+      </x:c>
+      <x:c r="O54" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P54" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="Q54" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="R54" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S54" t="str">
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>Ipamorelin</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>Growth Hormone Support</x:v>
+      </x:c>
+      <x:c r="D55" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E55" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+      <x:c r="F55" t="n">
+        <x:v>0.16999999999999993</x:v>
+      </x:c>
+      <x:c r="G55" t="n">
+        <x:v>0.03399999999999999</x:v>
+      </x:c>
+      <x:c r="H55" t="n">
+        <x:v>99.34</x:v>
+      </x:c>
+      <x:c r="I55" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J55" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L55" t="str">
+        <x:v>RPT-2026-822844</x:v>
+      </x:c>
+      <x:c r="M55" t="str">
+        <x:v>SGX-VP-2026-0728-U21</x:v>
+      </x:c>
+      <x:c r="N55" t="str">
+        <x:v>IP260725A</x:v>
+      </x:c>
+      <x:c r="O55" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P55" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="Q55" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="R55" t="str">
+        <x:v>White flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S55" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str">
+        <x:v>COA-0043</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D56" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E56" t="n">
+        <x:v>10.36</x:v>
+      </x:c>
+      <x:c r="F56" t="n">
+        <x:v>0.35999999999999943</x:v>
+      </x:c>
+      <x:c r="G56" t="n">
+        <x:v>0.03599999999999994</x:v>
+      </x:c>
+      <x:c r="H56" t="n">
+        <x:v>99.41</x:v>
+      </x:c>
+      <x:c r="I56" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J56" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K56" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L56" t="str">
+        <x:v>RPT-2026-932680</x:v>
+      </x:c>
+      <x:c r="M56" t="str">
+        <x:v>SGX-VP-2026-0728-G60</x:v>
+      </x:c>
+      <x:c r="N56" t="str">
+        <x:v>RT260725A</x:v>
+      </x:c>
+      <x:c r="O56" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P56" t="str">
+        <x:v>Copper</x:v>
+      </x:c>
+      <x:c r="Q56" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="R56" t="str">
+        <x:v>Clear flip-off cap with copper aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S56" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="str">
+        <x:v>COA-0044</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>Amylin / Weight</x:v>
+      </x:c>
+      <x:c r="D57" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E57" t="n">
+        <x:v>4.63</x:v>
+      </x:c>
+      <x:c r="F57" t="n">
+        <x:v>-0.3700000000000001</x:v>
+      </x:c>
+      <x:c r="G57" t="n">
+        <x:v>-0.07400000000000002</x:v>
+      </x:c>
+      <x:c r="H57" t="n">
+        <x:v>99.67</x:v>
+      </x:c>
+      <x:c r="I57" t="str">
+        <x:v>Underfilled</x:v>
+      </x:c>
+      <x:c r="J57" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K57" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="L57" t="str">
+        <x:v>Elor5-20260731S0925</x:v>
+      </x:c>
+      <x:c r="M57" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N57" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="O57" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P57" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="Q57" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="R57" t="str">
+        <x:v>Crimp/cap color not listed in the testing record.</x:v>
+      </x:c>
+      <x:c r="S57" t="str">
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str">
+        <x:v>COA-0045</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>CJC-1295</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>GHRH analog</x:v>
+      </x:c>
+      <x:c r="D58" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E58" t="n">
+        <x:v>10.52</x:v>
+      </x:c>
+      <x:c r="F58" t="n">
+        <x:v>0.5199999999999996</x:v>
+      </x:c>
+      <x:c r="G58" t="n">
+        <x:v>0.051999999999999956</x:v>
+      </x:c>
+      <x:c r="H58" t="n">
+        <x:v>99.72</x:v>
+      </x:c>
+      <x:c r="I58" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J58" t="str">
+        <x:v>ILS Laboratories</x:v>
+      </x:c>
+      <x:c r="K58" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="L58" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="M58" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N58" t="str">
+        <x:v>CND10-2606</x:v>
+      </x:c>
+      <x:c r="O58" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P58" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="Q58" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="R58" t="str">
+        <x:v>Crimp/cap color not listed or visible in the supplied COA image.</x:v>
+      </x:c>
+      <x:c r="S58" t="str">
+        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str">
+        <x:v>COA-0046</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>Metabolic / Cellular Energy</x:v>
+      </x:c>
+      <x:c r="D59" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E59" t="n">
+        <x:v>488.47</x:v>
+      </x:c>
+      <x:c r="F59" t="n">
+        <x:v>-11.529999999999973</x:v>
+      </x:c>
+      <x:c r="G59" t="n">
+        <x:v>-0.023059999999999945</x:v>
+      </x:c>
+      <x:c r="H59" t="n">
+        <x:v>99.549</x:v>
+      </x:c>
+      <x:c r="I59" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J59" t="str">
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K59" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="L59" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="M59" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N59" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O59" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P59" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="Q59" t="str">
+        <x:v>Black</x:v>
+      </x:c>
+      <x:c r="R59" t="str">
+        <x:v>Black flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S59" t="str">
+        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5558,7 +6160,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>assets/coa/KLOW80mg-02.pdf</x:v>
+        <x:v>assets/coa/documents/freedom-diagnostics/klow-80mg/KLOW80mg-02.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5703,7 +6305,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/COA RPT-2026-237183 - SteriGenix.pdf</x:v>
+        <x:v>assets/coa/documents/sterigenix/bpc-157-tb-500-blend/COA-RPT-2026-237183-SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5848,7 +6450,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/COA RPT-2026-442015 - SteriGenix.pdf</x:v>
+        <x:v>assets/coa/documents/sterigenix/tirzepatide/COA-RPT-2026-442015-SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5993,7 +6595,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/COA RPT-2026-538821 - SteriGenix.pdf</x:v>
+        <x:v>assets/coa/documents/sterigenix/semaglutide/COA-RPT-2026-538821-SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6138,7 +6740,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/COA RPT-2026-654610 - SteriGenix.pdf</x:v>
+        <x:v>assets/coa/documents/sterigenix/bpc-157/COA-RPT-2026-654610-SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8109,7 +8711,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P29" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/bpc-tb-blend/PT-BPCTB-10-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q29" s="14" t="str">
         <x:v>Pass</x:v>
@@ -8177,7 +8779,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P30" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/mots-c/PT-MOTS-40-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q30" s="14" t="str">
         <x:v>Pass</x:v>
@@ -8245,7 +8847,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P31" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-20-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-20-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q31" s="14" t="str">
         <x:v>Pass</x:v>
@@ -8313,7 +8915,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P32" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-30-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-30-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q32" s="14" t="str">
         <x:v>Pass</x:v>
@@ -8585,7 +9187,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P36" s="14" t="str">
-        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
+        <x:v>Local image: assets/coa/images/freedom-diagnostics/ghk-cu/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
       </x:c>
       <x:c r="Q36" s="14" t="str">
         <x:v>Pass</x:v>
@@ -8721,7 +9323,7 @@
         <x:v>BB260725A</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157-tb-500-blend/COA-RPT-2026-237183-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q38" t="str">
         <x:v>Pass</x:v>
@@ -8789,7 +9391,7 @@
         <x:v>TR260725A</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/tirzepatide/COA-RPT-2026-442015-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q39" t="str">
         <x:v>Pass</x:v>
@@ -8857,7 +9459,7 @@
         <x:v>SM260725A</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/semaglutide/COA-RPT-2026-538821-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q40" t="str">
         <x:v>Pass</x:v>
@@ -8925,7 +9527,7 @@
         <x:v>BC260725A</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157/COA-RPT-2026-654610-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q41" t="str">
         <x:v>Pass</x:v>
@@ -8993,7 +9595,7 @@
         <x:v>CU260725A</x:v>
       </x:c>
       <x:c r="P42" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ghk-cu/COA-RPT-2026-697297-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q42" t="str">
         <x:v>Pass</x:v>
@@ -9061,7 +9663,7 @@
         <x:v>IP260725A</x:v>
       </x:c>
       <x:c r="P43" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ipamorelin/COA-RPT-2026-822844-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q43" t="str">
         <x:v>Pass</x:v>
@@ -9129,7 +9731,7 @@
         <x:v>RT260725A</x:v>
       </x:c>
       <x:c r="P44" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/retatrutide/COA-RPT-2026-932680-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q44" t="str">
         <x:v>Pass</x:v>
@@ -9197,7 +9799,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="P45" t="str">
-        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/tianjin-qiangxin/eloralintide/Elor5-20260731S0925-report.pdf</x:v>
       </x:c>
       <x:c r="Q45" t="str">
         <x:v>Pass</x:v>
@@ -9216,6 +9818,142 @@
       </x:c>
       <x:c r="V45" t="str">
         <x:v>Crimp/cap color not listed in the testing record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>COA-0045</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>CJC-1295</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>GHRH analog</x:v>
+      </x:c>
+      <x:c r="D46" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E46" t="n">
+        <x:v>10.52</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>0.5199999999999996</x:v>
+      </x:c>
+      <x:c r="G46" t="n">
+        <x:v>0.051999999999999956</x:v>
+      </x:c>
+      <x:c r="H46" t="n">
+        <x:v>99.72</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>ILS Laboratories</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L46" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="M46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O46" t="str">
+        <x:v>CND10-2606</x:v>
+      </x:c>
+      <x:c r="P46" t="str">
+        <x:v>Local PDF: assets/coa/documents/ils-laboratories/cjc-1295/CJC-1295-10mg-2026-07-31-ILS.pdf</x:v>
+      </x:c>
+      <x:c r="Q46" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R46" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S46" t="str">
+        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
+      </x:c>
+      <x:c r="T46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="U46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="V46" t="str">
+        <x:v>Crimp/cap color not listed or visible in the supplied COA image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>COA-0046</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Metabolic / Cellular Energy</x:v>
+      </x:c>
+      <x:c r="D47" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E47" t="n">
+        <x:v>488.47</x:v>
+      </x:c>
+      <x:c r="F47" t="n">
+        <x:v>-11.529999999999973</x:v>
+      </x:c>
+      <x:c r="G47" t="n">
+        <x:v>-0.023059999999999945</x:v>
+      </x:c>
+      <x:c r="H47" t="n">
+        <x:v>99.549</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K47" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L47" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="M47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="P47" t="str">
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/nad-plus/NAD-500mg-2026-07-29-Kovera.pdf</x:v>
+      </x:c>
+      <x:c r="Q47" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R47" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S47" t="str">
+        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
+      </x:c>
+      <x:c r="T47" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U47" t="str">
+        <x:v>Black</x:v>
+      </x:c>
+      <x:c r="V47" t="str">
+        <x:v>Black flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9360,7 +10098,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/COA RPT-2026-697297 - SteriGenix.pdf</x:v>
+        <x:v>assets/coa/documents/sterigenix/ghk-cu/COA-RPT-2026-697297-SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9505,7 +10243,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/COA RPT-2026-822844 - SteriGenix.pdf</x:v>
+        <x:v>assets/coa/documents/sterigenix/ipamorelin/COA-RPT-2026-822844-SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9650,7 +10388,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/COA RPT-2026-932680 - SteriGenix.pdf</x:v>
+        <x:v>assets/coa/documents/sterigenix/retatrutide/COA-RPT-2026-932680-SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9795,7 +10533,401 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+        <x:v>assets/coa/documents/tianjin-qiangxin/eloralintide/Elor5-20260731S0925-report.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="62" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="22" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" s="22" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="12" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str">
+        <x:v>COA-0045</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="12" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="str">
+        <x:v>CJC-1295</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="12" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" s="12" t="str">
+        <x:v>GHRH analog</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="12" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" s="12" t="str">
+        <x:v>ILS Laboratories</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="12" t="str">
+        <x:v>COA #</x:v>
+      </x:c>
+      <x:c r="B6" s="12" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="12" t="str">
+        <x:v>Accession #</x:v>
+      </x:c>
+      <x:c r="B7" s="12" t="str">
+        <x:v>ACC-2026-10918</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="12" t="str">
+        <x:v>Analysis Date</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="12" t="str">
+        <x:v>Date Received</x:v>
+      </x:c>
+      <x:c r="B9" s="12" t="str">
+        <x:v>2026-07-17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="12" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B10" s="12" t="str">
+        <x:v>CND10-2606</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="12" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="12" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="n">
+        <x:v>10.52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B13" s="12" t="n">
+        <x:v>99.72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="12" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B14" s="12" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="12" t="str">
+        <x:v>Identity</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="str">
+        <x:v>Confirmed: CJC-1295 (HPLC-RTM)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="12" t="str">
+        <x:v>Fentanyl Screen</x:v>
+      </x:c>
+      <x:c r="B16" s="12" t="str">
+        <x:v>Not Detected</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="12" t="str">
+        <x:v>Sample Matrix</x:v>
+      </x:c>
+      <x:c r="B17" s="12" t="str">
+        <x:v>Lyophilized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="12" t="str">
+        <x:v>Volume</x:v>
+      </x:c>
+      <x:c r="B18" s="12" t="str">
+        <x:v>3 mL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="12" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B19" s="12" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="12" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B20" s="12" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="12" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B21" s="12" t="str">
+        <x:v>COA/access identifiers are redacted in the supplied certificate image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="12" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="str">
+        <x:v>assets/coa/documents/ils-laboratories/cjc-1295/CJC-1295-10mg-2026-07-31-ILS.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="62" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="22" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" s="22" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="12" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str">
+        <x:v>COA-0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="12" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="12" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" s="12" t="str">
+        <x:v>Metabolic / Cellular Energy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="12" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" s="12" t="str">
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="12" t="str">
+        <x:v>Certified</x:v>
+      </x:c>
+      <x:c r="B6" s="12" t="str">
+        <x:v>2026-07-29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="12" t="str">
+        <x:v>Report #</x:v>
+      </x:c>
+      <x:c r="B7" s="12" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="12" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="12" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" s="12" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="12" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" s="12" t="n">
+        <x:v>500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="12" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="n">
+        <x:v>488.47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="n">
+        <x:v>99.549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="12" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" s="12" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="12" t="str">
+        <x:v>Identity</x:v>
+      </x:c>
+      <x:c r="B14" s="12" t="str">
+        <x:v>Confirmed: NAD+ (LC-MS)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="12" t="str">
+        <x:v>CAS Number</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="str">
+        <x:v>53-84-9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="12" t="str">
+        <x:v>Molecular Formula</x:v>
+      </x:c>
+      <x:c r="B16" s="12" t="str">
+        <x:v>C21H27N7O14P2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="12" t="str">
+        <x:v>Endotoxin Safety Screen</x:v>
+      </x:c>
+      <x:c r="B17" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="12" t="str">
+        <x:v>Heavy Metals</x:v>
+      </x:c>
+      <x:c r="B18" s="12" t="str">
+        <x:v>Arsenic, Cadmium, Lead, Mercury: Negative</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="12" t="str">
+        <x:v>Vial 1</x:v>
+      </x:c>
+      <x:c r="B19" s="12" t="str">
+        <x:v>99.517% purity / 483.68 mg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="12" t="str">
+        <x:v>Vial 2</x:v>
+      </x:c>
+      <x:c r="B20" s="12" t="str">
+        <x:v>99.582% purity / 493.26 mg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="12" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B21" s="12" t="str">
+        <x:v>Black</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="12" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="12" t="str">
+        <x:v>Closure Notes</x:v>
+      </x:c>
+      <x:c r="B23" s="12" t="str">
+        <x:v>Black flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="12" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B24" s="12" t="str">
+        <x:v>assets/coa/documents/kovera-labs/nad-plus/NAD-500mg-2026-07-29-Kovera.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10620,43 +11752,43 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>COA-0007</x:v>
+        <x:v>COA-0045</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>CJC-1295</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>GHRH analog</x:v>
       </x:c>
       <x:c r="E19" s="14" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F19" s="14" t="n">
-        <x:v>26</x:v>
+        <x:v>10.52</x:v>
       </x:c>
       <x:c r="G19" s="16" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.051999999999999956</x:v>
       </x:c>
       <x:c r="H19" s="18" t="n">
-        <x:v>99.7</x:v>
+        <x:v>99.72</x:v>
       </x:c>
       <x:c r="I19" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J19" s="14" t="str">
-        <x:v>BT Labs</x:v>
+        <x:v>ILS Laboratories</x:v>
       </x:c>
       <x:c r="K19" s="14" t="n">
-        <x:v>46133</x:v>
+        <x:v>46234</x:v>
       </x:c>
       <x:c r="L19" s="14" t="str">
-        <x:v>Royal Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M19" s="14" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N19" s="14" t="str">
-        <x:v>20 mg label; 130.1% potency</x:v>
+        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -10664,7 +11796,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>COA-0008</x:v>
+        <x:v>COA-0007</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
         <x:v>Tirzepatide</x:v>
@@ -10673,13 +11805,13 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E20" s="14" t="n">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F20" s="14" t="n">
-        <x:v>46.6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G20" s="16" t="n">
-        <x:v>0.165</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="H20" s="18" t="n">
         <x:v>99.7</x:v>
@@ -10691,16 +11823,16 @@
         <x:v>BT Labs</x:v>
       </x:c>
       <x:c r="K20" s="14" t="n">
-        <x:v>46106</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="L20" s="14" t="str">
-        <x:v>Gray</x:v>
+        <x:v>Royal Blue</x:v>
       </x:c>
       <x:c r="M20" s="14" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N20" s="14" t="str">
-        <x:v>40 mg label; 116.4% potency</x:v>
+        <x:v>20 mg label; 130.1% potency</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -10708,43 +11840,43 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>COA-0044</x:v>
+        <x:v>COA-0008</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>Eloralintide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>Amylin / Weight</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E21" s="14" t="n">
-        <x:v>5</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F21" s="14" t="n">
-        <x:v>4.63</x:v>
+        <x:v>46.6</x:v>
       </x:c>
       <x:c r="G21" s="16" t="n">
-        <x:v>-0.07400000000000002</x:v>
+        <x:v>0.165</x:v>
       </x:c>
       <x:c r="H21" s="18" t="n">
-        <x:v>99.67</x:v>
+        <x:v>99.7</x:v>
       </x:c>
       <x:c r="I21" s="14" t="str">
-        <x:v>Underfilled</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J21" s="14" t="str">
-        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+        <x:v>BT Labs</x:v>
       </x:c>
       <x:c r="K21" s="14" t="n">
-        <x:v>46234</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L21" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Gray</x:v>
       </x:c>
       <x:c r="M21" s="14" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N21" s="14" t="str">
-        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+        <x:v>40 mg label; 116.4% potency</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -10752,34 +11884,34 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>COA-0003</x:v>
+        <x:v>COA-0044</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Eloralintide</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Amylin / Weight</x:v>
       </x:c>
       <x:c r="E22" s="14" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F22" s="14" t="n">
-        <x:v>6.63</x:v>
+        <x:v>4.63</x:v>
       </x:c>
       <x:c r="G22" s="16" t="n">
-        <x:v>0.326</x:v>
+        <x:v>-0.07400000000000002</x:v>
       </x:c>
       <x:c r="H22" s="18" t="n">
-        <x:v>99.654</x:v>
+        <x:v>99.67</x:v>
       </x:c>
       <x:c r="I22" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>Underfilled</x:v>
       </x:c>
       <x:c r="J22" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
       </x:c>
       <x:c r="K22" s="14" t="n">
-        <x:v>46174</x:v>
+        <x:v>46234</x:v>
       </x:c>
       <x:c r="L22" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -10788,7 +11920,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N22" s="14" t="str">
-        <x:v>Heavy metals negative; endotoxin pass</x:v>
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -10796,43 +11928,43 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>COA-0032</x:v>
+        <x:v>COA-0003</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>Semaglutide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E23" s="14" t="n">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F23" s="14" t="n">
-        <x:v>15.53</x:v>
+        <x:v>6.63</x:v>
       </x:c>
       <x:c r="G23" s="16" t="n">
-        <x:v>0.035333333333333335</x:v>
+        <x:v>0.326</x:v>
       </x:c>
       <x:c r="H23" s="18" t="n">
-        <x:v>99.642</x:v>
+        <x:v>99.654</x:v>
       </x:c>
       <x:c r="I23" s="14" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J23" s="14" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
-      <x:c r="K23" s="14" t="str">
-        <x:v>2026-07-03</x:v>
+      <x:c r="K23" s="14" t="n">
+        <x:v>46174</x:v>
       </x:c>
       <x:c r="L23" s="14" t="str">
-        <x:v>Black</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M23" s="14" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N23" s="14" t="str">
-        <x:v>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</x:v>
+        <x:v>Heavy metals negative; endotoxin pass</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -10840,28 +11972,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
-        <x:v>COA-0033</x:v>
+        <x:v>COA-0032</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Semaglutide</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E24" s="14" t="n">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F24" s="14" t="n">
-        <x:v>33.24</x:v>
+        <x:v>15.53</x:v>
       </x:c>
       <x:c r="G24" s="16" t="n">
-        <x:v>0.10800000000000001</x:v>
+        <x:v>0.035333333333333335</x:v>
       </x:c>
       <x:c r="H24" s="18" t="n">
-        <x:v>99.6</x:v>
+        <x:v>99.642</x:v>
       </x:c>
       <x:c r="I24" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J24" s="14" t="str">
         <x:v>Kovera Labs</x:v>
@@ -10870,13 +12002,13 @@
         <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L24" s="14" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M24" s="14" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N24" s="14" t="str">
-        <x:v>Kovera image COA; blue cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
+        <x:v>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -10884,43 +12016,43 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>COA-0020</x:v>
+        <x:v>COA-0033</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>KPV</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>Other</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E25" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F25" s="14" t="n">
-        <x:v>12.19</x:v>
+        <x:v>33.24</x:v>
       </x:c>
       <x:c r="G25" s="16" t="n">
-        <x:v>0.2189999999999999</x:v>
+        <x:v>0.10800000000000001</x:v>
       </x:c>
       <x:c r="H25" s="18" t="n">
-        <x:v>99.589</x:v>
+        <x:v>99.6</x:v>
       </x:c>
       <x:c r="I25" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J25" s="14" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K25" s="14" t="n">
-        <x:v>46057</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K25" s="14" t="str">
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L25" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M25" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N25" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>Kovera image COA; blue cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -10928,34 +12060,34 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>COA-0031</x:v>
+        <x:v>COA-0020</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>KPV</x:v>
       </x:c>
       <x:c r="D26" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Other</x:v>
       </x:c>
       <x:c r="E26" s="14" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F26" s="14" t="n">
-        <x:v>33.77</x:v>
+        <x:v>12.19</x:v>
       </x:c>
       <x:c r="G26" s="16" t="n">
-        <x:v>0.12566666666666668</x:v>
+        <x:v>0.2189999999999999</x:v>
       </x:c>
       <x:c r="H26" s="18" t="n">
-        <x:v>99.58</x:v>
+        <x:v>99.589</x:v>
       </x:c>
       <x:c r="I26" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J26" s="14" t="str">
-        <x:v>Testides</x:v>
-      </x:c>
-      <x:c r="K26" s="14" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K26" s="14" t="n">
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L26" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -10964,7 +12096,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N26" s="14" t="str">
-        <x:v>Retatrutide 30mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -10972,43 +12104,43 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
-        <x:v>COA-0040</x:v>
+        <x:v>COA-0031</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>BPC-157</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E27" s="14" t="n">
-        <x:v>5</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F27" s="14" t="n">
-        <x:v>5.13</x:v>
+        <x:v>33.77</x:v>
       </x:c>
       <x:c r="G27" s="16" t="n">
-        <x:v>0.025999999999999978</x:v>
+        <x:v>0.12566666666666668</x:v>
       </x:c>
       <x:c r="H27" s="18" t="n">
-        <x:v>99.57</x:v>
+        <x:v>99.58</x:v>
       </x:c>
       <x:c r="I27" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J27" s="14" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K27" s="14" t="n">
-        <x:v>46239</x:v>
+        <x:v>Testides</x:v>
+      </x:c>
+      <x:c r="K27" s="14" t="str">
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L27" s="14" t="str">
-        <x:v>Green</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M27" s="14" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N27" s="14" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Retatrutide 30mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -11016,43 +12148,43 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
-        <x:v>COA-0026</x:v>
+        <x:v>COA-0040</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>BPC-157</x:v>
       </x:c>
       <x:c r="D28" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
       <x:c r="E28" s="14" t="n">
-        <x:v>40</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F28" s="14" t="n">
-        <x:v>42.53</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="G28" s="16" t="n">
-        <x:v>0.06325</x:v>
+        <x:v>0.025999999999999978</x:v>
       </x:c>
       <x:c r="H28" s="18" t="n">
-        <x:v>99.569</x:v>
+        <x:v>99.57</x:v>
       </x:c>
       <x:c r="I28" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J28" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K28" s="14" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K28" s="14" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L28" s="14" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Green</x:v>
       </x:c>
       <x:c r="M28" s="14" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N28" s="14" t="str">
-        <x:v>Blue cap Retatrutide 40mg</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -11060,7 +12192,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
-        <x:v>COA-0025</x:v>
+        <x:v>COA-0026</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -11069,16 +12201,16 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E29" s="14" t="n">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F29" s="14" t="n">
-        <x:v>33.31</x:v>
+        <x:v>42.53</x:v>
       </x:c>
       <x:c r="G29" s="16" t="n">
-        <x:v>0.1103333333333333</x:v>
+        <x:v>0.06325</x:v>
       </x:c>
       <x:c r="H29" s="18" t="n">
-        <x:v>99.563</x:v>
+        <x:v>99.569</x:v>
       </x:c>
       <x:c r="I29" s="14" t="str">
         <x:v>Overfilled</x:v>
@@ -11090,13 +12222,13 @@
         <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="L29" s="14" t="str">
-        <x:v>Transparent</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M29" s="14" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N29" s="14" t="str">
-        <x:v>Transparent cap Retatrutide 30mg</x:v>
+        <x:v>Blue cap Retatrutide 40mg</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -11104,43 +12236,43 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
-        <x:v>COA-0038</x:v>
+        <x:v>COA-0025</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D30" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E30" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F30" s="14" t="n">
-        <x:v>10.09</x:v>
+        <x:v>33.31</x:v>
       </x:c>
       <x:c r="G30" s="16" t="n">
-        <x:v>0.008999999999999985</x:v>
+        <x:v>0.1103333333333333</x:v>
       </x:c>
       <x:c r="H30" s="18" t="n">
-        <x:v>99.52</x:v>
+        <x:v>99.563</x:v>
       </x:c>
       <x:c r="I30" s="14" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J30" s="14" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K30" s="14" t="n">
-        <x:v>46239</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K30" s="14" t="str">
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="L30" s="14" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Transparent</x:v>
       </x:c>
       <x:c r="M30" s="14" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N30" s="14" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Transparent cap Retatrutide 30mg</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -11148,43 +12280,43 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
-        <x:v>COA-0001</x:v>
+        <x:v>COA-0046</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>NAD+</x:v>
       </x:c>
       <x:c r="D31" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Metabolic / Cellular Energy</x:v>
       </x:c>
       <x:c r="E31" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="F31" s="14" t="n">
-        <x:v>11.8</x:v>
+        <x:v>488.47</x:v>
       </x:c>
       <x:c r="G31" s="16" t="n">
-        <x:v>0.1800000000000001</x:v>
+        <x:v>-0.023059999999999945</x:v>
       </x:c>
       <x:c r="H31" s="18" t="n">
-        <x:v>99.516</x:v>
+        <x:v>99.549</x:v>
       </x:c>
       <x:c r="I31" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J31" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K31" s="14" t="n">
-        <x:v>46156</x:v>
+        <x:v>46232</x:v>
       </x:c>
       <x:c r="L31" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M31" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N31" s="14" t="str">
-        <x:v>RT10 - common GLP-1 blind test; overfilled</x:v>
+        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -11192,39 +12324,43 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
-        <x:v>COA-0006</x:v>
+        <x:v>COA-0038</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D32" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
-      <x:c r="E32" s="14"/>
+      <x:c r="E32" s="14" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="F32" s="14" t="n">
-        <x:v>22.47</x:v>
-      </x:c>
-      <x:c r="G32" s="16"/>
+        <x:v>10.09</x:v>
+      </x:c>
+      <x:c r="G32" s="16" t="n">
+        <x:v>0.008999999999999985</x:v>
+      </x:c>
       <x:c r="H32" s="18" t="n">
-        <x:v>99.5</x:v>
+        <x:v>99.52</x:v>
       </x:c>
       <x:c r="I32" s="14" t="str">
-        <x:v>Review</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J32" s="14" t="str">
-        <x:v>Aminos Analytics</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="K32" s="14" t="n">
-        <x:v>46146</x:v>
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L32" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="M32" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N32" s="14" t="str">
-        <x:v>Labeled quantity unclear from image</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -11232,7 +12368,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="14" t="str">
-        <x:v>COA-0004</x:v>
+        <x:v>COA-0001</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -11241,25 +12377,25 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E33" s="14" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F33" s="14" t="n">
-        <x:v>17.93</x:v>
+        <x:v>11.8</x:v>
       </x:c>
       <x:c r="G33" s="16" t="n">
-        <x:v>0.1953333333333333</x:v>
+        <x:v>0.1800000000000001</x:v>
       </x:c>
       <x:c r="H33" s="18" t="n">
-        <x:v>99.491</x:v>
+        <x:v>99.516</x:v>
       </x:c>
       <x:c r="I33" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J33" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K33" s="14" t="n">
-        <x:v>46175</x:v>
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L33" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -11268,7 +12404,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N33" s="14" t="str">
-        <x:v>Heavy metals negative; endotoxin pass</x:v>
+        <x:v>RT10 - common GLP-1 blind test; overfilled</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -11276,7 +12412,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="14" t="str">
-        <x:v>COA-0030</x:v>
+        <x:v>COA-0006</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -11284,26 +12420,22 @@
       <x:c r="D34" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
-      <x:c r="E34" s="14" t="n">
-        <x:v>20</x:v>
-      </x:c>
+      <x:c r="E34" s="14"/>
       <x:c r="F34" s="14" t="n">
-        <x:v>21.4</x:v>
-      </x:c>
-      <x:c r="G34" s="16" t="n">
-        <x:v>0.06999999999999999</x:v>
-      </x:c>
+        <x:v>22.47</x:v>
+      </x:c>
+      <x:c r="G34" s="16"/>
       <x:c r="H34" s="18" t="n">
-        <x:v>99.49</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="I34" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>Review</x:v>
       </x:c>
       <x:c r="J34" s="14" t="str">
-        <x:v>Testides</x:v>
-      </x:c>
-      <x:c r="K34" s="14" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>Aminos Analytics</x:v>
+      </x:c>
+      <x:c r="K34" s="14" t="n">
+        <x:v>46146</x:v>
       </x:c>
       <x:c r="L34" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -11312,7 +12444,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N34" s="14" t="str">
-        <x:v>Retatrutide 20mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Labeled quantity unclear from image</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -11320,7 +12452,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="14" t="str">
-        <x:v>COA-0043</x:v>
+        <x:v>COA-0004</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -11329,34 +12461,34 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E35" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F35" s="14" t="n">
-        <x:v>10.36</x:v>
+        <x:v>17.93</x:v>
       </x:c>
       <x:c r="G35" s="16" t="n">
-        <x:v>0.03599999999999994</x:v>
+        <x:v>0.1953333333333333</x:v>
       </x:c>
       <x:c r="H35" s="18" t="n">
-        <x:v>99.41</x:v>
+        <x:v>99.491</x:v>
       </x:c>
       <x:c r="I35" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J35" s="14" t="str">
-        <x:v>SteriGenix</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K35" s="14" t="n">
-        <x:v>46239</x:v>
+        <x:v>46175</x:v>
       </x:c>
       <x:c r="L35" s="14" t="str">
-        <x:v>Clear</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M35" s="14" t="str">
-        <x:v>Copper</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N35" s="14" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Heavy metals negative; endotoxin pass</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -11364,25 +12496,25 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>COA-0029</x:v>
+        <x:v>COA-0030</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D36" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E36" t="n">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F36" t="n">
-        <x:v>45.03</x:v>
+        <x:v>21.4</x:v>
       </x:c>
       <x:c r="G36" t="n">
-        <x:v>0.12575</x:v>
+        <x:v>0.06999999999999999</x:v>
       </x:c>
       <x:c r="H36" t="n">
-        <x:v>99.39</x:v>
+        <x:v>99.49</x:v>
       </x:c>
       <x:c r="I36" t="str">
         <x:v>Overfilled</x:v>
@@ -11400,7 +12532,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N36" t="str">
-        <x:v>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Retatrutide 20mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -11408,7 +12540,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>COA-0002</x:v>
+        <x:v>COA-0043</x:v>
       </x:c>
       <x:c r="C37" t="str">
         <x:v>Retatrutide</x:v>
@@ -11420,31 +12552,31 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F37" t="n">
-        <x:v>10</x:v>
+        <x:v>10.36</x:v>
       </x:c>
       <x:c r="G37" t="n">
-        <x:v>0</x:v>
+        <x:v>0.03599999999999994</x:v>
       </x:c>
       <x:c r="H37" t="n">
-        <x:v>99.369</x:v>
+        <x:v>99.41</x:v>
       </x:c>
       <x:c r="I37" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J37" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="K37" t="n">
-        <x:v>46057</x:v>
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L37" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="M37" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Copper</x:v>
       </x:c>
       <x:c r="N37" t="str">
-        <x:v>On label</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -11452,43 +12584,43 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>COA-0042</x:v>
+        <x:v>COA-0029</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>Ipamorelin</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D38" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E38" t="n">
-        <x:v>5</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F38" t="n">
-        <x:v>5.17</x:v>
+        <x:v>45.03</x:v>
       </x:c>
       <x:c r="G38" t="n">
-        <x:v>0.03399999999999999</x:v>
+        <x:v>0.12575</x:v>
       </x:c>
       <x:c r="H38" t="n">
-        <x:v>99.34</x:v>
+        <x:v>99.39</x:v>
       </x:c>
       <x:c r="I38" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J38" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K38" t="n">
-        <x:v>46239</x:v>
+        <x:v>Testides</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L38" t="str">
-        <x:v>White</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M38" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N38" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -11496,43 +12628,43 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>COA-0039</x:v>
+        <x:v>COA-0002</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>Semaglutide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D39" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E39" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F39" t="n">
-        <x:v>5.07</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G39" t="n">
-        <x:v>0.014000000000000058</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H39" t="n">
-        <x:v>99.32</x:v>
+        <x:v>99.369</x:v>
       </x:c>
       <x:c r="I39" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J39" t="str">
-        <x:v>SteriGenix</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K39" t="n">
-        <x:v>46239</x:v>
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L39" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M39" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N39" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>On label</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -11540,25 +12672,25 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>COA-0037</x:v>
+        <x:v>COA-0042</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>BPC-157 / TB-500 Blend</x:v>
+        <x:v>Ipamorelin</x:v>
       </x:c>
       <x:c r="D40" t="str">
-        <x:v>Healing / Recovery Blend</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E40" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F40" t="n">
-        <x:v>10.55</x:v>
+        <x:v>5.17</x:v>
       </x:c>
       <x:c r="G40" t="n">
-        <x:v>0.05500000000000007</x:v>
+        <x:v>0.03399999999999999</x:v>
       </x:c>
       <x:c r="H40" t="n">
-        <x:v>99.13</x:v>
+        <x:v>99.34</x:v>
       </x:c>
       <x:c r="I40" t="str">
         <x:v>Overfilled</x:v>
@@ -11570,13 +12702,13 @@
         <x:v>46239</x:v>
       </x:c>
       <x:c r="L40" t="str">
-        <x:v>Red</x:v>
+        <x:v>White</x:v>
       </x:c>
       <x:c r="M40" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N40" t="str">
-        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -11584,43 +12716,43 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>COA-0016</x:v>
+        <x:v>COA-0039</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>Semaglutide</x:v>
       </x:c>
       <x:c r="D41" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E41" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F41" t="n">
-        <x:v>11.38</x:v>
+        <x:v>5.07</x:v>
       </x:c>
       <x:c r="G41" t="n">
-        <x:v>0.1380000000000001</x:v>
+        <x:v>0.014000000000000058</x:v>
       </x:c>
       <x:c r="H41" t="n">
-        <x:v>99.085</x:v>
+        <x:v>99.32</x:v>
       </x:c>
       <x:c r="I41" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J41" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="K41" t="n">
-        <x:v>46155</x:v>
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L41" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M41" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N41" t="str">
-        <x:v>TB-500 / TB4</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -11628,43 +12760,43 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" t="str">
-        <x:v>COA-0014</x:v>
+        <x:v>COA-0037</x:v>
       </x:c>
       <x:c r="C42" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>BPC-157 / TB-500 Blend</x:v>
       </x:c>
       <x:c r="D42" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Healing / Recovery Blend</x:v>
       </x:c>
       <x:c r="E42" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F42" t="n">
-        <x:v>11.17</x:v>
+        <x:v>10.55</x:v>
       </x:c>
       <x:c r="G42" t="n">
-        <x:v>0.117</x:v>
+        <x:v>0.05500000000000007</x:v>
       </x:c>
       <x:c r="H42" t="n">
-        <x:v>99.055</x:v>
+        <x:v>99.13</x:v>
       </x:c>
       <x:c r="I42" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J42" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="K42" t="n">
-        <x:v>46155</x:v>
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L42" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Red</x:v>
       </x:c>
       <x:c r="M42" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N42" t="str">
-        <x:v>MS10 / MOTS-C</x:v>
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -11672,28 +12804,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" t="str">
-        <x:v>COA-0011</x:v>
+        <x:v>COA-0016</x:v>
       </x:c>
       <x:c r="C43" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>TB-500</x:v>
       </x:c>
       <x:c r="D43" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
       <x:c r="E43" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F43" t="n">
-        <x:v>10.47</x:v>
+        <x:v>11.38</x:v>
       </x:c>
       <x:c r="G43" t="n">
-        <x:v>0.04700000000000006</x:v>
+        <x:v>0.1380000000000001</x:v>
       </x:c>
       <x:c r="H43" t="n">
-        <x:v>99.04</x:v>
+        <x:v>99.085</x:v>
       </x:c>
       <x:c r="I43" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J43" t="str">
         <x:v>Janoshik</x:v>
@@ -11708,7 +12840,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N43" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>TB-500 / TB4</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -11716,24 +12848,26 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" t="str">
-        <x:v>COA-0017</x:v>
+        <x:v>COA-0014</x:v>
       </x:c>
       <x:c r="C44" t="str">
-        <x:v>BPC-157</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D44" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E44" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F44" t="n">
-        <x:v>5.54</x:v>
+        <x:v>11.17</x:v>
       </x:c>
       <x:c r="G44" t="n">
-        <x:v>0.108</x:v>
-      </x:c>
-      <x:c r="H44"/>
+        <x:v>0.117</x:v>
+      </x:c>
+      <x:c r="H44" t="n">
+        <x:v>99.055</x:v>
+      </x:c>
       <x:c r="I44" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
@@ -11741,7 +12875,7 @@
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K44" t="n">
-        <x:v>46057</x:v>
+        <x:v>46155</x:v>
       </x:c>
       <x:c r="L44" t="str">
         <x:v>Not Listed</x:v>
@@ -11750,7 +12884,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N44" t="str">
-        <x:v>Blend report BPC5+TB5</x:v>
+        <x:v>MS10 / MOTS-C</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -11758,24 +12892,26 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" t="str">
-        <x:v>COA-0018</x:v>
+        <x:v>COA-0011</x:v>
       </x:c>
       <x:c r="C45" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>Cagrilintide</x:v>
       </x:c>
       <x:c r="D45" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E45" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F45" t="n">
-        <x:v>5.43</x:v>
+        <x:v>10.47</x:v>
       </x:c>
       <x:c r="G45" t="n">
-        <x:v>0.08599999999999994</x:v>
-      </x:c>
-      <x:c r="H45"/>
+        <x:v>0.04700000000000006</x:v>
+      </x:c>
+      <x:c r="H45" t="n">
+        <x:v>99.04</x:v>
+      </x:c>
       <x:c r="I45" t="str">
         <x:v>On label</x:v>
       </x:c>
@@ -11783,15 +12919,99 @@
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K45" t="n">
+        <x:v>46155</x:v>
+      </x:c>
+      <x:c r="L45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>COA-0017</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="E46" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>5.54</x:v>
+      </x:c>
+      <x:c r="G46" t="n">
+        <x:v>0.108</x:v>
+      </x:c>
+      <x:c r="H46"/>
+      <x:c r="I46" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K46" t="n">
         <x:v>46057</x:v>
       </x:c>
-      <x:c r="L45" t="str">
-        <x:v>Not Listed</x:v>
-      </x:c>
-      <x:c r="M45" t="str">
-        <x:v>Not Listed</x:v>
-      </x:c>
-      <x:c r="N45" t="str">
+      <x:c r="L46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
+        <x:v>Blend report BPC5+TB5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>COA-0018</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>TB-500</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="E47" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F47" t="n">
+        <x:v>5.43</x:v>
+      </x:c>
+      <x:c r="G47" t="n">
+        <x:v>0.08599999999999994</x:v>
+      </x:c>
+      <x:c r="H47"/>
+      <x:c r="I47" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K47" t="n">
+        <x:v>46057</x:v>
+      </x:c>
+      <x:c r="L47" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M47" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N47" t="str">
         <x:v>Blend report BPC5+TB5</x:v>
       </x:c>
     </x:row>
@@ -13763,7 +14983,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P29" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/bpc-tb-blend/PT-BPCTB-10-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q29" s="14" t="str">
         <x:v>Pass</x:v>
@@ -13831,7 +15051,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P30" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/mots-c/PT-MOTS-40-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q30" s="14" t="str">
         <x:v>Pass</x:v>
@@ -13899,7 +15119,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P31" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-20-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-20-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q31" s="14" t="str">
         <x:v>Pass</x:v>
@@ -13967,7 +15187,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P32" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-30-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-30-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q32" s="14" t="str">
         <x:v>Pass</x:v>
@@ -14239,7 +15459,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P36" s="14" t="str">
-        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
+        <x:v>Local image: assets/coa/images/freedom-diagnostics/ghk-cu/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
       </x:c>
       <x:c r="Q36" s="14" t="str">
         <x:v>Pass</x:v>
@@ -14375,7 +15595,7 @@
         <x:v>BB260725A</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157-tb-500-blend/COA-RPT-2026-237183-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q38" t="str">
         <x:v>Pass</x:v>
@@ -14443,7 +15663,7 @@
         <x:v>TR260725A</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/tirzepatide/COA-RPT-2026-442015-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q39" t="str">
         <x:v>Pass</x:v>
@@ -14511,7 +15731,7 @@
         <x:v>SM260725A</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/semaglutide/COA-RPT-2026-538821-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q40" t="str">
         <x:v>Pass</x:v>
@@ -14579,7 +15799,7 @@
         <x:v>BC260725A</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157/COA-RPT-2026-654610-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q41" t="str">
         <x:v>Pass</x:v>
@@ -14647,7 +15867,7 @@
         <x:v>CU260725A</x:v>
       </x:c>
       <x:c r="P42" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ghk-cu/COA-RPT-2026-697297-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q42" t="str">
         <x:v>Pass</x:v>
@@ -14715,7 +15935,7 @@
         <x:v>IP260725A</x:v>
       </x:c>
       <x:c r="P43" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ipamorelin/COA-RPT-2026-822844-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q43" t="str">
         <x:v>Pass</x:v>
@@ -14783,7 +16003,7 @@
         <x:v>RT260725A</x:v>
       </x:c>
       <x:c r="P44" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/retatrutide/COA-RPT-2026-932680-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q44" t="str">
         <x:v>Pass</x:v>
@@ -14851,7 +16071,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="P45" t="str">
-        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/tianjin-qiangxin/eloralintide/Elor5-20260731S0925-report.pdf</x:v>
       </x:c>
       <x:c r="Q45" t="str">
         <x:v>Pass</x:v>
@@ -14870,6 +16090,142 @@
       </x:c>
       <x:c r="V45" t="str">
         <x:v>Crimp/cap color not listed in the testing record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>COA-0045</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>CJC-1295</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>GHRH analog</x:v>
+      </x:c>
+      <x:c r="D46" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E46" t="n">
+        <x:v>10.52</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>0.5199999999999996</x:v>
+      </x:c>
+      <x:c r="G46" t="n">
+        <x:v>0.051999999999999956</x:v>
+      </x:c>
+      <x:c r="H46" t="n">
+        <x:v>99.72</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>ILS Laboratories</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L46" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="M46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O46" t="str">
+        <x:v>CND10-2606</x:v>
+      </x:c>
+      <x:c r="P46" t="str">
+        <x:v>Local PDF: assets/coa/documents/ils-laboratories/cjc-1295/CJC-1295-10mg-2026-07-31-ILS.pdf</x:v>
+      </x:c>
+      <x:c r="Q46" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R46" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S46" t="str">
+        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
+      </x:c>
+      <x:c r="T46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="U46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="V46" t="str">
+        <x:v>Crimp/cap color not listed or visible in the supplied COA image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>COA-0046</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Metabolic / Cellular Energy</x:v>
+      </x:c>
+      <x:c r="D47" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E47" t="n">
+        <x:v>488.47</x:v>
+      </x:c>
+      <x:c r="F47" t="n">
+        <x:v>-11.529999999999973</x:v>
+      </x:c>
+      <x:c r="G47" t="n">
+        <x:v>-0.023059999999999945</x:v>
+      </x:c>
+      <x:c r="H47" t="n">
+        <x:v>99.549</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K47" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L47" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="M47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="P47" t="str">
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/nad-plus/NAD-500mg-2026-07-29-Kovera.pdf</x:v>
+      </x:c>
+      <x:c r="Q47" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R47" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S47" t="str">
+        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
+      </x:c>
+      <x:c r="T47" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U47" t="str">
+        <x:v>Black</x:v>
+      </x:c>
+      <x:c r="V47" t="str">
+        <x:v>Black flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14903,16 +16259,16 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Aminos Analytics</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>Retatrutide, Tirzepatide 30, Cagrilintide, AOD-9604, MOTS-C, TB-500, BPC-157, SS-31, KPV, CJC-1295 No DAC</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>Janoshik task number + verify key</x:v>
+        <x:v>Aminos certificate</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>Task/report numbers preserved in COA Database</x:v>
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -14920,55 +16276,111 @@
         <x:v>BT Labs</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
-        <x:v>Tirzepatide 20, Tirzepatide 40, Tirzepatide 60</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
         <x:v>BT Labs report number</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
-        <x:v>BT Labs reports use IF-824-QSA-TR006 report IDs</x:v>
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
-        <x:v>Retatrutide 5, Retatrutide 10 / Trivial-3R, Retatrutide 15</x:v>
+        <x:v>GHK-Cu, KLOW 80mg, Retatrutide</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>Kovera certificate</x:v>
+        <x:v>Freedom Diagnostics accession/search code + COA PDF</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
-        <x:v>Heavy metals/endotoxin screening shown on certificates</x:v>
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
-        <x:v>Aminos Analytics</x:v>
+        <x:v>ILS Laboratories</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>CJC-1295</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
-        <x:v>Aminos certificate</x:v>
+        <x:v>ILS Laboratories certificate / HPLC report</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>Labeled quantity unclear in image; marked N/A/unclear</x:v>
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>Retatrutide 20mg, KLOW 80mg</x:v>
+        <x:v>AOD-9604, BPC-157, CJC-1295 No DAC, Cagrilintide, KPV, MOTS-C, Retatrutide, SS-31, TB-500, Tirzepatide</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
-        <x:v>Freedom Diagnostics accession/search code + COA PDF</x:v>
+        <x:v>Janoshik task number + verify key</x:v>
       </x:c>
       <x:c r="D6" s="14" t="str">
-        <x:v>Accession and search code preserved; vial closure colors documented from COA image.</x:v>
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>NAD+, Retatrutide, Semaglutide, Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Kovera certificate</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>ADAMAX, BPC-157, BPC-157 / TB-500 Blend, GHK-Cu, Ipamorelin, Retatrutide, Semaglutide, Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>SteriGenix report/task number + verification key + COA PDF</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Testides</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>BPC/TB Blend, MOTS-C, Retatrutide</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Testides report image / certificate</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>Partner laboratory report PDF</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16769,7 +18181,7 @@
         <x:v>da424443</x:v>
       </x:c>
       <x:c r="P29" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/bpc-tb-blend/PT-BPCTB-10-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q29" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -16831,7 +18243,7 @@
         <x:v>96ea8238</x:v>
       </x:c>
       <x:c r="P30" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/mots-c/PT-MOTS-40-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q30" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -16893,7 +18305,7 @@
         <x:v>5c1aa528</x:v>
       </x:c>
       <x:c r="P31" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-20-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-20-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q31" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -16955,7 +18367,7 @@
         <x:v>a8c10db6</x:v>
       </x:c>
       <x:c r="P32" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-30-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-30-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q32" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -17203,7 +18615,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P36" s="14" t="str">
-        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
+        <x:v>Local image: assets/coa/images/freedom-diagnostics/ghk-cu/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
       </x:c>
       <x:c r="Q36" s="14" t="str">
         <x:v>Clear/Transparent</x:v>
@@ -17327,7 +18739,7 @@
         <x:v>SGX-VP-2026-0728-G37</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157-tb-500-blend/COA-RPT-2026-237183-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q38" t="str">
         <x:v>Red</x:v>
@@ -17389,7 +18801,7 @@
         <x:v>SGX-VP-2026-0728-K72</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/tirzepatide/COA-RPT-2026-442015-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q39" t="str">
         <x:v>Yellow</x:v>
@@ -17451,7 +18863,7 @@
         <x:v>SGX-VP-2026-0728-U17</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/semaglutide/COA-RPT-2026-538821-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q40" t="str">
         <x:v>Blue</x:v>
@@ -17513,7 +18925,7 @@
         <x:v>SGX-VP-2026-0728-Z53</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157/COA-RPT-2026-654610-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q41" t="str">
         <x:v>Green</x:v>
@@ -17575,7 +18987,7 @@
         <x:v>SGX-VP-2026-0728-K16</x:v>
       </x:c>
       <x:c r="P42" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ghk-cu/COA-RPT-2026-697297-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q42" t="str">
         <x:v>Blue</x:v>
@@ -17637,7 +19049,7 @@
         <x:v>SGX-VP-2026-0728-U21</x:v>
       </x:c>
       <x:c r="P43" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ipamorelin/COA-RPT-2026-822844-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q43" t="str">
         <x:v>White</x:v>
@@ -17699,7 +19111,7 @@
         <x:v>SGX-VP-2026-0728-G60</x:v>
       </x:c>
       <x:c r="P44" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/retatrutide/COA-RPT-2026-932680-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q44" t="str">
         <x:v>Clear</x:v>
@@ -17761,7 +19173,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="P45" t="str">
-        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/tianjin-qiangxin/eloralintide/Elor5-20260731S0925-report.pdf</x:v>
       </x:c>
       <x:c r="Q45" t="str">
         <x:v>Not Listed</x:v>
@@ -17774,6 +19186,130 @@
       </x:c>
       <x:c r="T45" t="str">
         <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>COA-0045</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>CJC-1295</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>GHRH analog</x:v>
+      </x:c>
+      <x:c r="D46" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E46" t="n">
+        <x:v>10.52</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>0.5199999999999996</x:v>
+      </x:c>
+      <x:c r="G46" t="n">
+        <x:v>0.051999999999999956</x:v>
+      </x:c>
+      <x:c r="H46" t="n">
+        <x:v>99.72</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>CND10-2606</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>ILS Laboratories</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L46" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="M46" t="str">
+        <x:v>COA-0045</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="P46" t="str">
+        <x:v>Local PDF: assets/coa/documents/ils-laboratories/cjc-1295/CJC-1295-10mg-2026-07-31-ILS.pdf</x:v>
+      </x:c>
+      <x:c r="Q46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="R46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="S46" t="str">
+        <x:v>Crimp/cap color not listed or visible in the supplied COA image.</x:v>
+      </x:c>
+      <x:c r="T46" t="str">
+        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>COA-0046</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Metabolic / Cellular Energy</x:v>
+      </x:c>
+      <x:c r="D47" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E47" t="n">
+        <x:v>488.47</x:v>
+      </x:c>
+      <x:c r="F47" t="n">
+        <x:v>-11.529999999999973</x:v>
+      </x:c>
+      <x:c r="G47" t="n">
+        <x:v>-0.023059999999999945</x:v>
+      </x:c>
+      <x:c r="H47" t="n">
+        <x:v>99.549</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K47" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="L47" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="M47" t="str">
+        <x:v>COA-0046</x:v>
+      </x:c>
+      <x:c r="N47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="P47" t="str">
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/nad-plus/NAD-500mg-2026-07-29-Kovera.pdf</x:v>
+      </x:c>
+      <x:c r="Q47" t="str">
+        <x:v>Black</x:v>
+      </x:c>
+      <x:c r="R47" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="S47" t="str">
+        <x:v>Black flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T47" t="str">
+        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -19632,7 +21168,7 @@
         <x:v>da424443</x:v>
       </x:c>
       <x:c r="G29" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/bpc-tb-blend/PT-BPCTB-10-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H29" s="14" t="str">
         <x:v>Yes</x:v>
@@ -19697,7 +21233,7 @@
         <x:v>96ea8238</x:v>
       </x:c>
       <x:c r="G30" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/mots-c/PT-MOTS-40-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H30" s="14" t="str">
         <x:v>Yes</x:v>
@@ -19762,7 +21298,7 @@
         <x:v>5c1aa528</x:v>
       </x:c>
       <x:c r="G31" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-20-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-20-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H31" s="14" t="str">
         <x:v>Yes</x:v>
@@ -19827,7 +21363,7 @@
         <x:v>a8c10db6</x:v>
       </x:c>
       <x:c r="G32" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-30-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-30-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H32" s="14" t="str">
         <x:v>Yes</x:v>
@@ -20087,7 +21623,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="G36" s="14" t="str">
-        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
+        <x:v>Local image: assets/coa/images/freedom-diagnostics/ghk-cu/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
       </x:c>
       <x:c r="H36" s="14" t="str">
         <x:v>Yes</x:v>
@@ -20217,7 +21753,7 @@
         <x:v>SGX-VP-2026-0728-G37</x:v>
       </x:c>
       <x:c r="G38" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157-tb-500-blend/COA-RPT-2026-237183-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="H38" t="str">
         <x:v>Yes</x:v>
@@ -20282,7 +21818,7 @@
         <x:v>SGX-VP-2026-0728-K72</x:v>
       </x:c>
       <x:c r="G39" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/tirzepatide/COA-RPT-2026-442015-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="H39" t="str">
         <x:v>Yes</x:v>
@@ -20347,7 +21883,7 @@
         <x:v>SGX-VP-2026-0728-U17</x:v>
       </x:c>
       <x:c r="G40" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/semaglutide/COA-RPT-2026-538821-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="H40" t="str">
         <x:v>Yes</x:v>
@@ -20412,7 +21948,7 @@
         <x:v>SGX-VP-2026-0728-Z53</x:v>
       </x:c>
       <x:c r="G41" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157/COA-RPT-2026-654610-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="H41" t="str">
         <x:v>Yes</x:v>
@@ -20477,7 +22013,7 @@
         <x:v>SGX-VP-2026-0728-K16</x:v>
       </x:c>
       <x:c r="G42" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ghk-cu/COA-RPT-2026-697297-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="H42" t="str">
         <x:v>Yes</x:v>
@@ -20542,7 +22078,7 @@
         <x:v>SGX-VP-2026-0728-U21</x:v>
       </x:c>
       <x:c r="G43" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ipamorelin/COA-RPT-2026-822844-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="H43" t="str">
         <x:v>Yes</x:v>
@@ -20607,7 +22143,7 @@
         <x:v>SGX-VP-2026-0728-G60</x:v>
       </x:c>
       <x:c r="G44" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/retatrutide/COA-RPT-2026-932680-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="H44" t="str">
         <x:v>Yes</x:v>
@@ -20672,7 +22208,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="G45" t="str">
-        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/tianjin-qiangxin/eloralintide/Elor5-20260731S0925-report.pdf</x:v>
       </x:c>
       <x:c r="H45" t="str">
         <x:v>Yes</x:v>
@@ -20715,6 +22251,136 @@
       </x:c>
       <x:c r="U45" t="str">
         <x:v>Crimp/cap color not listed in the testing record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>COA-0045</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>CJC-1295</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>GHRH analog</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>ILS Laboratories</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>Local PDF: assets/coa/documents/ils-laboratories/cjc-1295/CJC-1295-10mg-2026-07-31-ILS.pdf</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I46" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J46" t="n">
+        <x:v>10.52</x:v>
+      </x:c>
+      <x:c r="K46" t="n">
+        <x:v>0.5199999999999996</x:v>
+      </x:c>
+      <x:c r="L46" t="n">
+        <x:v>0.051999999999999956</x:v>
+      </x:c>
+      <x:c r="M46" t="n">
+        <x:v>99.72</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O46" t="str">
+        <x:v>CND10-2606</x:v>
+      </x:c>
+      <x:c r="P46" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="Q46" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R46" t="str">
+        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
+      </x:c>
+      <x:c r="S46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="T46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="U46" t="str">
+        <x:v>Crimp/cap color not listed or visible in the supplied COA image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>COA-0046</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Metabolic / Cellular Energy</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="G47" t="str">
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/nad-plus/NAD-500mg-2026-07-29-Kovera.pdf</x:v>
+      </x:c>
+      <x:c r="H47" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I47" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J47" t="n">
+        <x:v>488.47</x:v>
+      </x:c>
+      <x:c r="K47" t="n">
+        <x:v>-11.529999999999973</x:v>
+      </x:c>
+      <x:c r="L47" t="n">
+        <x:v>-0.023059999999999945</x:v>
+      </x:c>
+      <x:c r="M47" t="n">
+        <x:v>99.549</x:v>
+      </x:c>
+      <x:c r="N47" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="O47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="P47" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="Q47" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R47" t="str">
+        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
+      </x:c>
+      <x:c r="S47" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="T47" t="str">
+        <x:v>Black</x:v>
+      </x:c>
+      <x:c r="U47" t="str">
+        <x:v>Black flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -20811,7 +22477,7 @@
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="F4" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>GHRH analog</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -20819,7 +22485,7 @@
         <x:v>BPC-157 / TB-500 Blend</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>ILS Laboratories</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
         <x:v>Underfilled</x:v>
@@ -20829,7 +22495,7 @@
       </x:c>
       <x:c r="E5" s="14"/>
       <x:c r="F5" s="14" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -20837,7 +22503,7 @@
         <x:v>BPC/TB Blend</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="C6" s="14"/>
       <x:c r="D6" s="14" t="str">
@@ -20845,15 +22511,15 @@
       </x:c>
       <x:c r="E6" s="14"/>
       <x:c r="F6" s="14" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
-        <x:v>CJC-1295 No DAC</x:v>
+        <x:v>CJC-1295</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
-        <x:v>SteriGenix</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="C7" s="14"/>
       <x:c r="D7" s="14" t="str">
@@ -20861,15 +22527,15 @@
       </x:c>
       <x:c r="E7" s="14"/>
       <x:c r="F7" s="14" t="str">
-        <x:v>Healing / Recovery Blend</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>CJC-1295 No DAC</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>Testides</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="C8" s="14"/>
       <x:c r="D8" s="14" t="str">
@@ -20877,15 +22543,15 @@
       </x:c>
       <x:c r="E8" s="14"/>
       <x:c r="F8" s="14" t="str">
-        <x:v>Metabolic / Fat Loss</x:v>
+        <x:v>Healing / Recovery Blend</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
-        <x:v>Eloralintide</x:v>
+        <x:v>Cagrilintide</x:v>
       </x:c>
       <x:c r="B9" s="14" t="str">
-        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+        <x:v>Testides</x:v>
       </x:c>
       <x:c r="C9" s="14"/>
       <x:c r="D9" s="14" t="str">
@@ -20893,26 +22559,28 @@
       </x:c>
       <x:c r="E9" s="14"/>
       <x:c r="F9" s="14" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Metabolic / Cellular Energy</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
-        <x:v>GHK-Cu</x:v>
-      </x:c>
-      <x:c r="B10" s="14"/>
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
       <x:c r="C10" s="14"/>
       <x:c r="D10" s="14" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="E10" s="14"/>
       <x:c r="F10" s="14" t="str">
-        <x:v>Other</x:v>
+        <x:v>Metabolic / Fat Loss</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14" t="str">
-        <x:v>Ipamorelin</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="B11" s="14"/>
       <x:c r="C11" s="14"/>
@@ -20921,12 +22589,12 @@
       </x:c>
       <x:c r="E11" s="14"/>
       <x:c r="F11" s="14" t="str">
-        <x:v>Regenerative / Skin</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="str">
-        <x:v>KLOW 80mg</x:v>
+        <x:v>Ipamorelin</x:v>
       </x:c>
       <x:c r="B12" s="14"/>
       <x:c r="C12" s="14"/>
@@ -20935,12 +22603,12 @@
       </x:c>
       <x:c r="E12" s="14"/>
       <x:c r="F12" s="14" t="str">
-        <x:v>Research Peptide</x:v>
+        <x:v>Other</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="14" t="str">
-        <x:v>KPV</x:v>
+        <x:v>KLOW 80mg</x:v>
       </x:c>
       <x:c r="B13" s="14"/>
       <x:c r="C13" s="14"/>
@@ -20948,11 +22616,13 @@
         <x:v>Royal Blue</x:v>
       </x:c>
       <x:c r="E13" s="14"/>
-      <x:c r="F13" s="14"/>
+      <x:c r="F13" s="14" t="str">
+        <x:v>Regenerative / Skin</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="14" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>KPV</x:v>
       </x:c>
       <x:c r="B14" s="14"/>
       <x:c r="C14" s="14"/>
@@ -20960,11 +22630,13 @@
         <x:v>Transparent</x:v>
       </x:c>
       <x:c r="E14" s="14"/>
-      <x:c r="F14" s="14"/>
+      <x:c r="F14" s="14" t="str">
+        <x:v>Research Peptide</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="B15" s="14"/>
       <x:c r="C15" s="14"/>
@@ -20976,7 +22648,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>SS-31</x:v>
+        <x:v>NAD+</x:v>
       </x:c>
       <x:c r="B16"/>
       <x:c r="C16"/>
@@ -20988,7 +22660,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>Semaglutide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="B17"/>
       <x:c r="C17"/>
@@ -20998,7 +22670,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>SS-31</x:v>
       </x:c>
       <x:c r="B18"/>
       <x:c r="C18"/>
@@ -21008,13 +22680,33 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Semaglutide</x:v>
       </x:c>
       <x:c r="B19"/>
       <x:c r="C19"/>
       <x:c r="D19"/>
       <x:c r="E19"/>
       <x:c r="F19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>TB-500</x:v>
+      </x:c>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
